--- a/bot検討用.xlsx
+++ b/bot検討用.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://daigakuseikyou-my.sharepoint.com/personal/yoshinaga_yoichiro_univ_coop/Documents/職員共有/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F20F8E27-31B3-4FEB-8F87-517869C7023C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{F20F8E27-31B3-4FEB-8F87-517869C7023C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CEFA59F-90AA-423B-ACB4-FD3610E09D7B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{02FBB63D-D231-44F9-B7EE-84B3A40B1B71}"/>
   </bookViews>
@@ -10304,7 +10304,7 @@
         <v>1131</v>
       </c>
       <c r="F492">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.45">
@@ -10324,7 +10324,7 @@
         <v>954</v>
       </c>
       <c r="F493">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.45">
@@ -10344,7 +10344,7 @@
         <v>974</v>
       </c>
       <c r="F494">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.45">
@@ -10364,7 +10364,7 @@
         <v>934</v>
       </c>
       <c r="F495">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.45">
@@ -10384,7 +10384,7 @@
         <v>870</v>
       </c>
       <c r="F496">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.45">
@@ -10404,7 +10404,7 @@
         <v>520</v>
       </c>
       <c r="F497">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.45">
@@ -10424,7 +10424,7 @@
         <v>822</v>
       </c>
       <c r="F498">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.45">
@@ -10444,7 +10444,7 @@
         <v>1037</v>
       </c>
       <c r="F499">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.45">
@@ -10464,7 +10464,7 @@
         <v>1190</v>
       </c>
       <c r="F500">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.45">
@@ -10484,7 +10484,7 @@
         <v>536</v>
       </c>
       <c r="F501">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.45">
@@ -10504,7 +10504,7 @@
         <v>883</v>
       </c>
       <c r="F502">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.45">
@@ -10524,7 +10524,7 @@
         <v>1210</v>
       </c>
       <c r="F503">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.45">
@@ -10544,7 +10544,7 @@
         <v>1227</v>
       </c>
       <c r="F504">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.45">
@@ -10564,7 +10564,7 @@
         <v>1019</v>
       </c>
       <c r="F505">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.45">
@@ -10584,7 +10584,7 @@
         <v>1117</v>
       </c>
       <c r="F506">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="507" spans="1:6" x14ac:dyDescent="0.45">
@@ -10604,7 +10604,7 @@
         <v>642</v>
       </c>
       <c r="F507">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="508" spans="1:6" x14ac:dyDescent="0.45">
@@ -10624,7 +10624,7 @@
         <v>1204</v>
       </c>
       <c r="F508">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="509" spans="1:6" x14ac:dyDescent="0.45">
@@ -10644,7 +10644,7 @@
         <v>1134</v>
       </c>
       <c r="F509">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="510" spans="1:6" x14ac:dyDescent="0.45">
@@ -10664,7 +10664,7 @@
         <v>672</v>
       </c>
       <c r="F510">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="511" spans="1:6" x14ac:dyDescent="0.45">
@@ -10684,7 +10684,7 @@
         <v>651</v>
       </c>
       <c r="F511">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="512" spans="1:6" x14ac:dyDescent="0.45">
@@ -10704,7 +10704,7 @@
         <v>1228</v>
       </c>
       <c r="F512">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="513" spans="1:6" x14ac:dyDescent="0.45">
@@ -10724,7 +10724,7 @@
         <v>638</v>
       </c>
       <c r="F513">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="514" spans="1:6" x14ac:dyDescent="0.45">
@@ -10744,7 +10744,7 @@
         <v>1033</v>
       </c>
       <c r="F514">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="515" spans="1:6" x14ac:dyDescent="0.45">
@@ -10764,7 +10764,7 @@
         <v>655</v>
       </c>
       <c r="F515">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="516" spans="1:6" x14ac:dyDescent="0.45">
@@ -10784,7 +10784,7 @@
         <v>1150</v>
       </c>
       <c r="F516">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="517" spans="1:6" x14ac:dyDescent="0.45">
@@ -10804,7 +10804,7 @@
         <v>1236</v>
       </c>
       <c r="F517">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="518" spans="1:6" x14ac:dyDescent="0.45">
@@ -10824,7 +10824,7 @@
         <v>841</v>
       </c>
       <c r="F518">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="519" spans="1:6" x14ac:dyDescent="0.45">
@@ -10844,7 +10844,7 @@
         <v>916</v>
       </c>
       <c r="F519">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="520" spans="1:6" x14ac:dyDescent="0.45">
@@ -10864,7 +10864,7 @@
         <v>668</v>
       </c>
       <c r="F520">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="521" spans="1:6" x14ac:dyDescent="0.45">
@@ -10884,7 +10884,7 @@
         <v>430</v>
       </c>
       <c r="F521">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="522" spans="1:6" x14ac:dyDescent="0.45">
@@ -10904,7 +10904,7 @@
         <v>548</v>
       </c>
       <c r="F522">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="523" spans="1:6" x14ac:dyDescent="0.45">
@@ -10924,7 +10924,7 @@
         <v>1083</v>
       </c>
       <c r="F523">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="524" spans="1:6" x14ac:dyDescent="0.45">
@@ -10944,7 +10944,7 @@
         <v>1064</v>
       </c>
       <c r="F524">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="525" spans="1:6" x14ac:dyDescent="0.45">
@@ -10964,7 +10964,7 @@
         <v>1151</v>
       </c>
       <c r="F525">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="526" spans="1:6" x14ac:dyDescent="0.45">
@@ -10984,7 +10984,7 @@
         <v>1081</v>
       </c>
       <c r="F526">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="527" spans="1:6" x14ac:dyDescent="0.45">
@@ -11004,7 +11004,7 @@
         <v>1176</v>
       </c>
       <c r="F527">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="528" spans="1:6" x14ac:dyDescent="0.45">
@@ -11024,7 +11024,7 @@
         <v>683</v>
       </c>
       <c r="F528">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="529" spans="1:6" x14ac:dyDescent="0.45">
@@ -11044,7 +11044,7 @@
         <v>650</v>
       </c>
       <c r="F529">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="530" spans="1:6" x14ac:dyDescent="0.45">
@@ -11064,7 +11064,7 @@
         <v>1063</v>
       </c>
       <c r="F530">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="531" spans="1:6" x14ac:dyDescent="0.45">
@@ -11084,7 +11084,7 @@
         <v>887</v>
       </c>
       <c r="F531">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="532" spans="1:6" x14ac:dyDescent="0.45">
@@ -11104,7 +11104,7 @@
         <v>1030</v>
       </c>
       <c r="F532">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.45">
@@ -11124,7 +11124,7 @@
         <v>1031</v>
       </c>
       <c r="F533">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="534" spans="1:6" x14ac:dyDescent="0.45">
@@ -11144,7 +11144,7 @@
         <v>589</v>
       </c>
       <c r="F534">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="535" spans="1:6" x14ac:dyDescent="0.45">
@@ -11164,7 +11164,7 @@
         <v>1178</v>
       </c>
       <c r="F535">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="536" spans="1:6" x14ac:dyDescent="0.45">
@@ -11184,7 +11184,7 @@
         <v>1157</v>
       </c>
       <c r="F536">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="537" spans="1:6" x14ac:dyDescent="0.45">
@@ -11204,7 +11204,7 @@
         <v>463</v>
       </c>
       <c r="F537">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="538" spans="1:6" x14ac:dyDescent="0.45">
@@ -11224,7 +11224,7 @@
         <v>637</v>
       </c>
       <c r="F538">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="539" spans="1:6" x14ac:dyDescent="0.45">
@@ -11244,7 +11244,7 @@
         <v>992</v>
       </c>
       <c r="F539">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="540" spans="1:6" x14ac:dyDescent="0.45">
@@ -11264,7 +11264,7 @@
         <v>1130</v>
       </c>
       <c r="F540">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="541" spans="1:6" x14ac:dyDescent="0.45">
@@ -11284,7 +11284,7 @@
         <v>751</v>
       </c>
       <c r="F541">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="542" spans="1:6" x14ac:dyDescent="0.45">
@@ -11304,7 +11304,7 @@
         <v>881</v>
       </c>
       <c r="F542">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="543" spans="1:6" x14ac:dyDescent="0.45">
@@ -11324,7 +11324,7 @@
         <v>1109</v>
       </c>
       <c r="F543">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="544" spans="1:6" x14ac:dyDescent="0.45">
@@ -11344,7 +11344,7 @@
         <v>1116</v>
       </c>
       <c r="F544">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="545" spans="1:6" x14ac:dyDescent="0.45">
@@ -11364,7 +11364,7 @@
         <v>513</v>
       </c>
       <c r="F545">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="546" spans="1:6" x14ac:dyDescent="0.45">
@@ -11384,7 +11384,7 @@
         <v>701</v>
       </c>
       <c r="F546">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="547" spans="1:6" x14ac:dyDescent="0.45">
@@ -11404,7 +11404,7 @@
         <v>610</v>
       </c>
       <c r="F547">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="548" spans="1:6" x14ac:dyDescent="0.45">
@@ -11424,7 +11424,7 @@
         <v>598</v>
       </c>
       <c r="F548">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="549" spans="1:6" x14ac:dyDescent="0.45">
@@ -11444,7 +11444,7 @@
         <v>838</v>
       </c>
       <c r="F549">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="550" spans="1:6" x14ac:dyDescent="0.45">
@@ -11464,7 +11464,7 @@
         <v>1016</v>
       </c>
       <c r="F550">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="551" spans="1:6" x14ac:dyDescent="0.45">
@@ -11484,7 +11484,7 @@
         <v>1200</v>
       </c>
       <c r="F551">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="552" spans="1:6" x14ac:dyDescent="0.45">
@@ -11504,7 +11504,7 @@
         <v>1079</v>
       </c>
       <c r="F552">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="553" spans="1:6" x14ac:dyDescent="0.45">
@@ -11524,7 +11524,7 @@
         <v>479</v>
       </c>
       <c r="F553">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="554" spans="1:6" x14ac:dyDescent="0.45">
@@ -11544,7 +11544,7 @@
         <v>1238</v>
       </c>
       <c r="F554">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="555" spans="1:6" x14ac:dyDescent="0.45">
@@ -11564,7 +11564,7 @@
         <v>569</v>
       </c>
       <c r="F555">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="556" spans="1:6" x14ac:dyDescent="0.45">
@@ -11584,7 +11584,7 @@
         <v>1066</v>
       </c>
       <c r="F556">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="557" spans="1:6" x14ac:dyDescent="0.45">
@@ -11604,7 +11604,7 @@
         <v>859</v>
       </c>
       <c r="F557">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="558" spans="1:6" x14ac:dyDescent="0.45">
@@ -11624,7 +11624,7 @@
         <v>928</v>
       </c>
       <c r="F558">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="559" spans="1:6" x14ac:dyDescent="0.45">
@@ -11644,7 +11644,7 @@
         <v>543</v>
       </c>
       <c r="F559">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="560" spans="1:6" x14ac:dyDescent="0.45">
@@ -11664,7 +11664,7 @@
         <v>718</v>
       </c>
       <c r="F560">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="561" spans="1:6" x14ac:dyDescent="0.45">
@@ -11684,7 +11684,7 @@
         <v>674</v>
       </c>
       <c r="F561">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="562" spans="1:6" x14ac:dyDescent="0.45">
@@ -11704,7 +11704,7 @@
         <v>847</v>
       </c>
       <c r="F562">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="563" spans="1:6" x14ac:dyDescent="0.45">
@@ -11724,7 +11724,7 @@
         <v>644</v>
       </c>
       <c r="F563">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="564" spans="1:6" x14ac:dyDescent="0.45">
@@ -11744,7 +11744,7 @@
         <v>581</v>
       </c>
       <c r="F564">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="565" spans="1:6" x14ac:dyDescent="0.45">
@@ -11764,7 +11764,7 @@
         <v>1195</v>
       </c>
       <c r="F565">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="566" spans="1:6" x14ac:dyDescent="0.45">
@@ -11784,7 +11784,7 @@
         <v>895</v>
       </c>
       <c r="F566">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="567" spans="1:6" x14ac:dyDescent="0.45">
@@ -11804,7 +11804,7 @@
         <v>781</v>
       </c>
       <c r="F567">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="568" spans="1:6" x14ac:dyDescent="0.45">
@@ -11824,7 +11824,7 @@
         <v>1229</v>
       </c>
       <c r="F568">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="569" spans="1:6" x14ac:dyDescent="0.45">
@@ -11844,7 +11844,7 @@
         <v>1158</v>
       </c>
       <c r="F569">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="570" spans="1:6" x14ac:dyDescent="0.45">
@@ -11864,7 +11864,7 @@
         <v>1205</v>
       </c>
       <c r="F570">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="571" spans="1:6" x14ac:dyDescent="0.45">
@@ -11884,7 +11884,7 @@
         <v>993</v>
       </c>
       <c r="F571">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="572" spans="1:6" x14ac:dyDescent="0.45">
@@ -11904,7 +11904,7 @@
         <v>768</v>
       </c>
       <c r="F572">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="573" spans="1:6" x14ac:dyDescent="0.45">
@@ -11924,7 +11924,7 @@
         <v>1164</v>
       </c>
       <c r="F573">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="574" spans="1:6" x14ac:dyDescent="0.45">
@@ -11944,7 +11944,7 @@
         <v>607</v>
       </c>
       <c r="F574">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="575" spans="1:6" x14ac:dyDescent="0.45">
@@ -11964,7 +11964,7 @@
         <v>905</v>
       </c>
       <c r="F575">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="576" spans="1:6" x14ac:dyDescent="0.45">
@@ -11984,7 +11984,7 @@
         <v>1188</v>
       </c>
       <c r="F576">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="577" spans="1:6" x14ac:dyDescent="0.45">
@@ -12004,7 +12004,7 @@
         <v>677</v>
       </c>
       <c r="F577">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="578" spans="1:6" x14ac:dyDescent="0.45">
@@ -12024,7 +12024,7 @@
         <v>542</v>
       </c>
       <c r="F578">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="579" spans="1:6" x14ac:dyDescent="0.45">
@@ -12044,7 +12044,7 @@
         <v>752</v>
       </c>
       <c r="F579">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="580" spans="1:6" x14ac:dyDescent="0.45">
@@ -12064,7 +12064,7 @@
         <v>1038</v>
       </c>
       <c r="F580">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="581" spans="1:6" x14ac:dyDescent="0.45">
@@ -12084,7 +12084,7 @@
         <v>549</v>
       </c>
       <c r="F581">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="582" spans="1:6" x14ac:dyDescent="0.45">
@@ -12104,7 +12104,7 @@
         <v>713</v>
       </c>
       <c r="F582">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="583" spans="1:6" x14ac:dyDescent="0.45">
@@ -12124,7 +12124,7 @@
         <v>1026</v>
       </c>
       <c r="F583">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="584" spans="1:6" x14ac:dyDescent="0.45">
@@ -12144,7 +12144,7 @@
         <v>1050</v>
       </c>
       <c r="F584">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="585" spans="1:6" x14ac:dyDescent="0.45">
@@ -12164,7 +12164,7 @@
         <v>941</v>
       </c>
       <c r="F585">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="586" spans="1:6" x14ac:dyDescent="0.45">
@@ -12184,7 +12184,7 @@
         <v>833</v>
       </c>
       <c r="F586">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="587" spans="1:6" x14ac:dyDescent="0.45">
@@ -12204,7 +12204,7 @@
         <v>446</v>
       </c>
       <c r="F587">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="588" spans="1:6" x14ac:dyDescent="0.45">
@@ -12224,7 +12224,7 @@
         <v>947</v>
       </c>
       <c r="F588">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="589" spans="1:6" x14ac:dyDescent="0.45">
@@ -12244,7 +12244,7 @@
         <v>739</v>
       </c>
       <c r="F589">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="590" spans="1:6" x14ac:dyDescent="0.45">
@@ -12264,7 +12264,7 @@
         <v>565</v>
       </c>
       <c r="F590">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="591" spans="1:6" x14ac:dyDescent="0.45">
@@ -12284,7 +12284,7 @@
         <v>689</v>
       </c>
       <c r="F591">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="592" spans="1:6" x14ac:dyDescent="0.45">
@@ -12304,7 +12304,7 @@
         <v>1111</v>
       </c>
       <c r="F592">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="593" spans="1:6" x14ac:dyDescent="0.45">
@@ -12324,7 +12324,7 @@
         <v>473</v>
       </c>
       <c r="F593">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="594" spans="1:6" x14ac:dyDescent="0.45">
@@ -12344,7 +12344,7 @@
         <v>1133</v>
       </c>
       <c r="F594">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="595" spans="1:6" x14ac:dyDescent="0.45">
@@ -12364,7 +12364,7 @@
         <v>783</v>
       </c>
       <c r="F595">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="596" spans="1:6" x14ac:dyDescent="0.45">
@@ -12384,7 +12384,7 @@
         <v>989</v>
       </c>
       <c r="F596">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="597" spans="1:6" x14ac:dyDescent="0.45">
@@ -12404,7 +12404,7 @@
         <v>502</v>
       </c>
       <c r="F597">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="598" spans="1:6" x14ac:dyDescent="0.45">
@@ -12424,7 +12424,7 @@
         <v>915</v>
       </c>
       <c r="F598">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="599" spans="1:6" x14ac:dyDescent="0.45">
@@ -12444,7 +12444,7 @@
         <v>1071</v>
       </c>
       <c r="F599">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="600" spans="1:6" x14ac:dyDescent="0.45">
@@ -12464,7 +12464,7 @@
         <v>740</v>
       </c>
       <c r="F600">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="601" spans="1:6" x14ac:dyDescent="0.45">
@@ -12484,7 +12484,7 @@
         <v>1163</v>
       </c>
       <c r="F601">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="602" spans="1:6" x14ac:dyDescent="0.45">
@@ -12504,7 +12504,7 @@
         <v>1054</v>
       </c>
       <c r="F602">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="603" spans="1:6" x14ac:dyDescent="0.45">
@@ -12524,7 +12524,7 @@
         <v>897</v>
       </c>
       <c r="F603">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="604" spans="1:6" x14ac:dyDescent="0.45">
@@ -12544,7 +12544,7 @@
         <v>458</v>
       </c>
       <c r="F604">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="605" spans="1:6" x14ac:dyDescent="0.45">
@@ -12564,7 +12564,7 @@
         <v>1093</v>
       </c>
       <c r="F605">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="606" spans="1:6" x14ac:dyDescent="0.45">
@@ -12584,7 +12584,7 @@
         <v>1044</v>
       </c>
       <c r="F606">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="607" spans="1:6" x14ac:dyDescent="0.45">
@@ -12604,7 +12604,7 @@
         <v>986</v>
       </c>
       <c r="F607">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="608" spans="1:6" x14ac:dyDescent="0.45">
@@ -12624,7 +12624,7 @@
         <v>587</v>
       </c>
       <c r="F608">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="609" spans="1:6" x14ac:dyDescent="0.45">
@@ -12644,7 +12644,7 @@
         <v>917</v>
       </c>
       <c r="F609">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="610" spans="1:6" x14ac:dyDescent="0.45">
@@ -12664,7 +12664,7 @@
         <v>678</v>
       </c>
       <c r="F610">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="611" spans="1:6" x14ac:dyDescent="0.45">
@@ -12684,7 +12684,7 @@
         <v>594</v>
       </c>
       <c r="F611">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="612" spans="1:6" x14ac:dyDescent="0.45">
@@ -12704,7 +12704,7 @@
         <v>508</v>
       </c>
       <c r="F612">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="613" spans="1:6" x14ac:dyDescent="0.45">
@@ -12724,7 +12724,7 @@
         <v>1080</v>
       </c>
       <c r="F613">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="614" spans="1:6" x14ac:dyDescent="0.45">
@@ -12744,7 +12744,7 @@
         <v>1010</v>
       </c>
       <c r="F614">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="615" spans="1:6" x14ac:dyDescent="0.45">
@@ -12764,7 +12764,7 @@
         <v>746</v>
       </c>
       <c r="F615">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="616" spans="1:6" x14ac:dyDescent="0.45">
@@ -12784,7 +12784,7 @@
         <v>819</v>
       </c>
       <c r="F616">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="617" spans="1:6" x14ac:dyDescent="0.45">
@@ -12804,7 +12804,7 @@
         <v>1225</v>
       </c>
       <c r="F617">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="618" spans="1:6" x14ac:dyDescent="0.45">
@@ -12824,7 +12824,7 @@
         <v>860</v>
       </c>
       <c r="F618">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="619" spans="1:6" x14ac:dyDescent="0.45">
@@ -12844,7 +12844,7 @@
         <v>924</v>
       </c>
       <c r="F619">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="620" spans="1:6" x14ac:dyDescent="0.45">
@@ -12864,7 +12864,7 @@
         <v>1179</v>
       </c>
       <c r="F620">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="621" spans="1:6" x14ac:dyDescent="0.45">
@@ -12884,7 +12884,7 @@
         <v>1011</v>
       </c>
       <c r="F621">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="622" spans="1:6" x14ac:dyDescent="0.45">
@@ -12904,7 +12904,7 @@
         <v>601</v>
       </c>
       <c r="F622">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="623" spans="1:6" x14ac:dyDescent="0.45">
@@ -12924,7 +12924,7 @@
         <v>1007</v>
       </c>
       <c r="F623">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="624" spans="1:6" x14ac:dyDescent="0.45">
@@ -12944,7 +12944,7 @@
         <v>439</v>
       </c>
       <c r="F624">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="625" spans="1:6" x14ac:dyDescent="0.45">
@@ -12964,7 +12964,7 @@
         <v>1208</v>
       </c>
       <c r="F625">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="626" spans="1:6" x14ac:dyDescent="0.45">
@@ -12984,7 +12984,7 @@
         <v>886</v>
       </c>
       <c r="F626">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="627" spans="1:6" x14ac:dyDescent="0.45">
@@ -13004,7 +13004,7 @@
         <v>540</v>
       </c>
       <c r="F627">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="628" spans="1:6" x14ac:dyDescent="0.45">
@@ -13024,7 +13024,7 @@
         <v>1119</v>
       </c>
       <c r="F628">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="629" spans="1:6" x14ac:dyDescent="0.45">
@@ -13044,7 +13044,7 @@
         <v>568</v>
       </c>
       <c r="F629">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="630" spans="1:6" x14ac:dyDescent="0.45">
@@ -13064,7 +13064,7 @@
         <v>763</v>
       </c>
       <c r="F630">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="631" spans="1:6" x14ac:dyDescent="0.45">
@@ -13084,7 +13084,7 @@
         <v>1005</v>
       </c>
       <c r="F631">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="632" spans="1:6" x14ac:dyDescent="0.45">
@@ -13104,7 +13104,7 @@
         <v>494</v>
       </c>
       <c r="F632">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="633" spans="1:6" x14ac:dyDescent="0.45">
@@ -13124,7 +13124,7 @@
         <v>1153</v>
       </c>
       <c r="F633">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="634" spans="1:6" x14ac:dyDescent="0.45">
@@ -13144,7 +13144,7 @@
         <v>911</v>
       </c>
       <c r="F634">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="635" spans="1:6" x14ac:dyDescent="0.45">
@@ -13164,7 +13164,7 @@
         <v>874</v>
       </c>
       <c r="F635">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="636" spans="1:6" x14ac:dyDescent="0.45">
@@ -13184,7 +13184,7 @@
         <v>665</v>
       </c>
       <c r="F636">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="637" spans="1:6" x14ac:dyDescent="0.45">
@@ -13204,7 +13204,7 @@
         <v>970</v>
       </c>
       <c r="F637">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="638" spans="1:6" x14ac:dyDescent="0.45">
@@ -13224,7 +13224,7 @@
         <v>489</v>
       </c>
       <c r="F638">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="639" spans="1:6" x14ac:dyDescent="0.45">
@@ -13244,7 +13244,7 @@
         <v>442</v>
       </c>
       <c r="F639">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="640" spans="1:6" x14ac:dyDescent="0.45">
@@ -13264,7 +13264,7 @@
         <v>832</v>
       </c>
       <c r="F640">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="641" spans="1:6" x14ac:dyDescent="0.45">
@@ -13284,7 +13284,7 @@
         <v>1170</v>
       </c>
       <c r="F641">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="642" spans="1:6" x14ac:dyDescent="0.45">
@@ -13304,7 +13304,7 @@
         <v>525</v>
       </c>
       <c r="F642">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="643" spans="1:6" x14ac:dyDescent="0.45">
@@ -13324,7 +13324,7 @@
         <v>898</v>
       </c>
       <c r="F643">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="644" spans="1:6" x14ac:dyDescent="0.45">
@@ -13344,7 +13344,7 @@
         <v>1103</v>
       </c>
       <c r="F644">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="645" spans="1:6" x14ac:dyDescent="0.45">
@@ -13364,7 +13364,7 @@
         <v>1101</v>
       </c>
       <c r="F645">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="646" spans="1:6" x14ac:dyDescent="0.45">
@@ -13384,7 +13384,7 @@
         <v>743</v>
       </c>
       <c r="F646">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="647" spans="1:6" x14ac:dyDescent="0.45">
@@ -13404,7 +13404,7 @@
         <v>816</v>
       </c>
       <c r="F647">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="648" spans="1:6" x14ac:dyDescent="0.45">
@@ -13424,7 +13424,7 @@
         <v>827</v>
       </c>
       <c r="F648">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="649" spans="1:6" x14ac:dyDescent="0.45">
@@ -13444,7 +13444,7 @@
         <v>1069</v>
       </c>
       <c r="F649">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="650" spans="1:6" x14ac:dyDescent="0.45">
@@ -13464,7 +13464,7 @@
         <v>1107</v>
       </c>
       <c r="F650">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="651" spans="1:6" x14ac:dyDescent="0.45">
@@ -13484,7 +13484,7 @@
         <v>1223</v>
       </c>
       <c r="F651">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="652" spans="1:6" x14ac:dyDescent="0.45">
@@ -13504,7 +13504,7 @@
         <v>588</v>
       </c>
       <c r="F652">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="653" spans="1:6" x14ac:dyDescent="0.45">
@@ -13524,7 +13524,7 @@
         <v>884</v>
       </c>
       <c r="F653">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="654" spans="1:6" x14ac:dyDescent="0.45">
@@ -13544,7 +13544,7 @@
         <v>813</v>
       </c>
       <c r="F654">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="655" spans="1:6" x14ac:dyDescent="0.45">
@@ -13564,7 +13564,7 @@
         <v>670</v>
       </c>
       <c r="F655">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="656" spans="1:6" x14ac:dyDescent="0.45">
@@ -13584,7 +13584,7 @@
         <v>880</v>
       </c>
       <c r="F656">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="657" spans="1:6" x14ac:dyDescent="0.45">
@@ -13604,7 +13604,7 @@
         <v>920</v>
       </c>
       <c r="F657">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="658" spans="1:6" x14ac:dyDescent="0.45">
@@ -13624,7 +13624,7 @@
         <v>1238</v>
       </c>
       <c r="F658">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="659" spans="1:6" x14ac:dyDescent="0.45">
@@ -13644,7 +13644,7 @@
         <v>909</v>
       </c>
       <c r="F659">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="660" spans="1:6" x14ac:dyDescent="0.45">
@@ -13664,7 +13664,7 @@
         <v>961</v>
       </c>
       <c r="F660">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="661" spans="1:6" x14ac:dyDescent="0.45">
@@ -13684,7 +13684,7 @@
         <v>717</v>
       </c>
       <c r="F661">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="662" spans="1:6" x14ac:dyDescent="0.45">
@@ -13704,7 +13704,7 @@
         <v>533</v>
       </c>
       <c r="F662">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="663" spans="1:6" x14ac:dyDescent="0.45">
@@ -13724,7 +13724,7 @@
         <v>957</v>
       </c>
       <c r="F663">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="664" spans="1:6" x14ac:dyDescent="0.45">
@@ -13744,7 +13744,7 @@
         <v>851</v>
       </c>
       <c r="F664">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="665" spans="1:6" x14ac:dyDescent="0.45">
@@ -13764,7 +13764,7 @@
         <v>868</v>
       </c>
       <c r="F665">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="666" spans="1:6" x14ac:dyDescent="0.45">
@@ -13784,7 +13784,7 @@
         <v>557</v>
       </c>
       <c r="F666">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="667" spans="1:6" x14ac:dyDescent="0.45">
@@ -13804,7 +13804,7 @@
         <v>737</v>
       </c>
       <c r="F667">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="668" spans="1:6" x14ac:dyDescent="0.45">
@@ -13824,7 +13824,7 @@
         <v>1162</v>
       </c>
       <c r="F668">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="669" spans="1:6" x14ac:dyDescent="0.45">
@@ -13844,7 +13844,7 @@
         <v>656</v>
       </c>
       <c r="F669">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="670" spans="1:6" x14ac:dyDescent="0.45">
@@ -13864,7 +13864,7 @@
         <v>744</v>
       </c>
       <c r="F670">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="671" spans="1:6" x14ac:dyDescent="0.45">
@@ -13884,7 +13884,7 @@
         <v>803</v>
       </c>
       <c r="F671">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="672" spans="1:6" x14ac:dyDescent="0.45">
@@ -13904,7 +13904,7 @@
         <v>791</v>
       </c>
       <c r="F672">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="673" spans="1:6" x14ac:dyDescent="0.45">
@@ -13924,7 +13924,7 @@
         <v>978</v>
       </c>
       <c r="F673">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="674" spans="1:6" x14ac:dyDescent="0.45">
@@ -13944,7 +13944,7 @@
         <v>927</v>
       </c>
       <c r="F674">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="675" spans="1:6" x14ac:dyDescent="0.45">
@@ -13964,7 +13964,7 @@
         <v>845</v>
       </c>
       <c r="F675">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="676" spans="1:6" x14ac:dyDescent="0.45">
@@ -13984,7 +13984,7 @@
         <v>705</v>
       </c>
       <c r="F676">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="677" spans="1:6" x14ac:dyDescent="0.45">
@@ -14004,7 +14004,7 @@
         <v>770</v>
       </c>
       <c r="F677">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="678" spans="1:6" x14ac:dyDescent="0.45">
@@ -14024,7 +14024,7 @@
         <v>437</v>
       </c>
       <c r="F678">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="679" spans="1:6" x14ac:dyDescent="0.45">
@@ -14044,7 +14044,7 @@
         <v>1058</v>
       </c>
       <c r="F679">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="680" spans="1:6" x14ac:dyDescent="0.45">
@@ -14064,7 +14064,7 @@
         <v>673</v>
       </c>
       <c r="F680">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="681" spans="1:6" x14ac:dyDescent="0.45">
@@ -14084,7 +14084,7 @@
         <v>631</v>
       </c>
       <c r="F681">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="682" spans="1:6" x14ac:dyDescent="0.45">
@@ -14104,7 +14104,7 @@
         <v>764</v>
       </c>
       <c r="F682">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="683" spans="1:6" x14ac:dyDescent="0.45">
@@ -14124,7 +14124,7 @@
         <v>590</v>
       </c>
       <c r="F683">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="684" spans="1:6" x14ac:dyDescent="0.45">
@@ -14144,7 +14144,7 @@
         <v>785</v>
       </c>
       <c r="F684">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="685" spans="1:6" x14ac:dyDescent="0.45">
@@ -14164,7 +14164,7 @@
         <v>926</v>
       </c>
       <c r="F685">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="686" spans="1:6" x14ac:dyDescent="0.45">
@@ -14184,7 +14184,7 @@
         <v>660</v>
       </c>
       <c r="F686">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="687" spans="1:6" x14ac:dyDescent="0.45">
@@ -14204,7 +14204,7 @@
         <v>481</v>
       </c>
       <c r="F687">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="688" spans="1:6" x14ac:dyDescent="0.45">
@@ -14224,7 +14224,7 @@
         <v>1215</v>
       </c>
       <c r="F688">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="689" spans="1:6" x14ac:dyDescent="0.45">
@@ -14244,7 +14244,7 @@
         <v>852</v>
       </c>
       <c r="F689">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="690" spans="1:6" x14ac:dyDescent="0.45">
@@ -14264,7 +14264,7 @@
         <v>649</v>
       </c>
       <c r="F690">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="691" spans="1:6" x14ac:dyDescent="0.45">
@@ -14284,7 +14284,7 @@
         <v>769</v>
       </c>
       <c r="F691">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="692" spans="1:6" x14ac:dyDescent="0.45">
@@ -14304,7 +14304,7 @@
         <v>885</v>
       </c>
       <c r="F692">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="693" spans="1:6" x14ac:dyDescent="0.45">
@@ -14324,7 +14324,7 @@
         <v>1199</v>
       </c>
       <c r="F693">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="694" spans="1:6" x14ac:dyDescent="0.45">
@@ -14344,7 +14344,7 @@
         <v>661</v>
       </c>
       <c r="F694">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="695" spans="1:6" x14ac:dyDescent="0.45">
@@ -14364,7 +14364,7 @@
         <v>1043</v>
       </c>
       <c r="F695">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="696" spans="1:6" x14ac:dyDescent="0.45">
@@ -14384,7 +14384,7 @@
         <v>648</v>
       </c>
       <c r="F696">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="697" spans="1:6" x14ac:dyDescent="0.45">
@@ -14404,7 +14404,7 @@
         <v>918</v>
       </c>
       <c r="F697">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="698" spans="1:6" x14ac:dyDescent="0.45">
@@ -14424,7 +14424,7 @@
         <v>940</v>
       </c>
       <c r="F698">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="699" spans="1:6" x14ac:dyDescent="0.45">
@@ -14444,7 +14444,7 @@
         <v>748</v>
       </c>
       <c r="F699">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="700" spans="1:6" x14ac:dyDescent="0.45">
@@ -14464,7 +14464,7 @@
         <v>1073</v>
       </c>
       <c r="F700">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="701" spans="1:6" x14ac:dyDescent="0.45">
@@ -14484,7 +14484,7 @@
         <v>1061</v>
       </c>
       <c r="F701">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="702" spans="1:6" x14ac:dyDescent="0.45">
@@ -14504,7 +14504,7 @@
         <v>583</v>
       </c>
       <c r="F702">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="703" spans="1:6" x14ac:dyDescent="0.45">
@@ -14524,7 +14524,7 @@
         <v>1014</v>
       </c>
       <c r="F703">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="704" spans="1:6" x14ac:dyDescent="0.45">
@@ -14544,7 +14544,7 @@
         <v>818</v>
       </c>
       <c r="F704">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="705" spans="1:6" x14ac:dyDescent="0.45">
@@ -14564,7 +14564,7 @@
         <v>855</v>
       </c>
       <c r="F705">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="706" spans="1:6" x14ac:dyDescent="0.45">
@@ -14584,7 +14584,7 @@
         <v>627</v>
       </c>
       <c r="F706">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="707" spans="1:6" x14ac:dyDescent="0.45">
@@ -14604,7 +14604,7 @@
         <v>1002</v>
       </c>
       <c r="F707">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="708" spans="1:6" x14ac:dyDescent="0.45">
@@ -14624,7 +14624,7 @@
         <v>534</v>
       </c>
       <c r="F708">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="709" spans="1:6" x14ac:dyDescent="0.45">
@@ -14644,7 +14644,7 @@
         <v>842</v>
       </c>
       <c r="F709">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="710" spans="1:6" x14ac:dyDescent="0.45">
@@ -14664,7 +14664,7 @@
         <v>820</v>
       </c>
       <c r="F710">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="711" spans="1:6" x14ac:dyDescent="0.45">
@@ -14684,7 +14684,7 @@
         <v>443</v>
       </c>
       <c r="F711">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="712" spans="1:6" x14ac:dyDescent="0.45">
@@ -14704,7 +14704,7 @@
         <v>900</v>
       </c>
       <c r="F712">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="713" spans="1:6" x14ac:dyDescent="0.45">
@@ -14724,7 +14724,7 @@
         <v>1175</v>
       </c>
       <c r="F713">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="714" spans="1:6" x14ac:dyDescent="0.45">
@@ -14744,7 +14744,7 @@
         <v>657</v>
       </c>
       <c r="F714">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="715" spans="1:6" x14ac:dyDescent="0.45">
@@ -14764,7 +14764,7 @@
         <v>1168</v>
       </c>
       <c r="F715">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="716" spans="1:6" x14ac:dyDescent="0.45">
@@ -14784,7 +14784,7 @@
         <v>685</v>
       </c>
       <c r="F716">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="717" spans="1:6" x14ac:dyDescent="0.45">
@@ -14804,7 +14804,7 @@
         <v>742</v>
       </c>
       <c r="F717">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="718" spans="1:6" x14ac:dyDescent="0.45">
@@ -14824,7 +14824,7 @@
         <v>939</v>
       </c>
       <c r="F718">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="719" spans="1:6" x14ac:dyDescent="0.45">
@@ -14844,7 +14844,7 @@
         <v>1039</v>
       </c>
       <c r="F719">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="720" spans="1:6" x14ac:dyDescent="0.45">
@@ -14864,7 +14864,7 @@
         <v>734</v>
       </c>
       <c r="F720">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="721" spans="1:6" x14ac:dyDescent="0.45">
@@ -14884,7 +14884,7 @@
         <v>1046</v>
       </c>
       <c r="F721">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="722" spans="1:6" x14ac:dyDescent="0.45">
@@ -14904,7 +14904,7 @@
         <v>980</v>
       </c>
       <c r="F722">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="723" spans="1:6" x14ac:dyDescent="0.45">
@@ -14924,7 +14924,7 @@
         <v>930</v>
       </c>
       <c r="F723">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="724" spans="1:6" x14ac:dyDescent="0.45">
@@ -14944,7 +14944,7 @@
         <v>676</v>
       </c>
       <c r="F724">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="725" spans="1:6" x14ac:dyDescent="0.45">
@@ -14964,7 +14964,7 @@
         <v>1165</v>
       </c>
       <c r="F725">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="726" spans="1:6" x14ac:dyDescent="0.45">
@@ -14984,7 +14984,7 @@
         <v>698</v>
       </c>
       <c r="F726">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="727" spans="1:6" x14ac:dyDescent="0.45">
@@ -15004,7 +15004,7 @@
         <v>552</v>
       </c>
       <c r="F727">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="728" spans="1:6" x14ac:dyDescent="0.45">
@@ -15024,7 +15024,7 @@
         <v>839</v>
       </c>
       <c r="F728">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="729" spans="1:6" x14ac:dyDescent="0.45">
@@ -15044,7 +15044,7 @@
         <v>653</v>
       </c>
       <c r="F729">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="730" spans="1:6" x14ac:dyDescent="0.45">
@@ -15064,7 +15064,7 @@
         <v>1187</v>
       </c>
       <c r="F730">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="731" spans="1:6" x14ac:dyDescent="0.45">
@@ -15084,7 +15084,7 @@
         <v>795</v>
       </c>
       <c r="F731">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="732" spans="1:6" x14ac:dyDescent="0.45">
@@ -15104,7 +15104,7 @@
         <v>836</v>
       </c>
       <c r="F732">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="733" spans="1:6" x14ac:dyDescent="0.45">
@@ -15124,7 +15124,7 @@
         <v>599</v>
       </c>
       <c r="F733">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="734" spans="1:6" x14ac:dyDescent="0.45">
@@ -15144,7 +15144,7 @@
         <v>1076</v>
       </c>
       <c r="F734">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="735" spans="1:6" x14ac:dyDescent="0.45">
@@ -15164,7 +15164,7 @@
         <v>1143</v>
       </c>
       <c r="F735">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="736" spans="1:6" x14ac:dyDescent="0.45">
@@ -15184,7 +15184,7 @@
         <v>1137</v>
       </c>
       <c r="F736">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="737" spans="1:6" x14ac:dyDescent="0.45">
@@ -15204,7 +15204,7 @@
         <v>1085</v>
       </c>
       <c r="F737">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="738" spans="1:6" x14ac:dyDescent="0.45">
@@ -15224,7 +15224,7 @@
         <v>461</v>
       </c>
       <c r="F738">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="739" spans="1:6" x14ac:dyDescent="0.45">
@@ -15244,7 +15244,7 @@
         <v>1154</v>
       </c>
       <c r="F739">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="740" spans="1:6" x14ac:dyDescent="0.45">
@@ -15264,7 +15264,7 @@
         <v>1024</v>
       </c>
       <c r="F740">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="741" spans="1:6" x14ac:dyDescent="0.45">
@@ -15284,7 +15284,7 @@
         <v>932</v>
       </c>
       <c r="F741">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="742" spans="1:6" x14ac:dyDescent="0.45">
@@ -15304,7 +15304,7 @@
         <v>603</v>
       </c>
       <c r="F742">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="743" spans="1:6" x14ac:dyDescent="0.45">
@@ -15324,7 +15324,7 @@
         <v>982</v>
       </c>
       <c r="F743">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="744" spans="1:6" x14ac:dyDescent="0.45">
@@ -15344,7 +15344,7 @@
         <v>1189</v>
       </c>
       <c r="F744">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="745" spans="1:6" x14ac:dyDescent="0.45">
@@ -15364,7 +15364,7 @@
         <v>1211</v>
       </c>
       <c r="F745">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="746" spans="1:6" x14ac:dyDescent="0.45">
@@ -15384,7 +15384,7 @@
         <v>1144</v>
       </c>
       <c r="F746">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="747" spans="1:6" x14ac:dyDescent="0.45">
@@ -15404,7 +15404,7 @@
         <v>1145</v>
       </c>
       <c r="F747">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="748" spans="1:6" x14ac:dyDescent="0.45">
@@ -15424,7 +15424,7 @@
         <v>1015</v>
       </c>
       <c r="F748">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="749" spans="1:6" x14ac:dyDescent="0.45">
@@ -15444,7 +15444,7 @@
         <v>537</v>
       </c>
       <c r="F749">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="750" spans="1:6" x14ac:dyDescent="0.45">
@@ -15464,7 +15464,7 @@
         <v>455</v>
       </c>
       <c r="F750">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="751" spans="1:6" x14ac:dyDescent="0.45">
@@ -15484,7 +15484,7 @@
         <v>1097</v>
       </c>
       <c r="F751">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="752" spans="1:6" x14ac:dyDescent="0.45">
@@ -15504,7 +15504,7 @@
         <v>721</v>
       </c>
       <c r="F752">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="753" spans="1:6" x14ac:dyDescent="0.45">
@@ -15524,7 +15524,7 @@
         <v>891</v>
       </c>
       <c r="F753">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="754" spans="1:6" x14ac:dyDescent="0.45">
@@ -15544,7 +15544,7 @@
         <v>944</v>
       </c>
       <c r="F754">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="755" spans="1:6" x14ac:dyDescent="0.45">
@@ -15564,7 +15564,7 @@
         <v>949</v>
       </c>
       <c r="F755">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="756" spans="1:6" x14ac:dyDescent="0.45">
@@ -15584,7 +15584,7 @@
         <v>907</v>
       </c>
       <c r="F756">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="757" spans="1:6" x14ac:dyDescent="0.45">
@@ -15604,7 +15604,7 @@
         <v>641</v>
       </c>
       <c r="F757">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="758" spans="1:6" x14ac:dyDescent="0.45">
@@ -15624,7 +15624,7 @@
         <v>574</v>
       </c>
       <c r="F758">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="759" spans="1:6" x14ac:dyDescent="0.45">
@@ -15644,7 +15644,7 @@
         <v>686</v>
       </c>
       <c r="F759">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="760" spans="1:6" x14ac:dyDescent="0.45">
@@ -15664,7 +15664,7 @@
         <v>613</v>
       </c>
       <c r="F760">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="761" spans="1:6" x14ac:dyDescent="0.45">
@@ -15684,7 +15684,7 @@
         <v>564</v>
       </c>
       <c r="F761">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="762" spans="1:6" x14ac:dyDescent="0.45">
@@ -15704,7 +15704,7 @@
         <v>459</v>
       </c>
       <c r="F762">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="763" spans="1:6" x14ac:dyDescent="0.45">
@@ -15724,7 +15724,7 @@
         <v>896</v>
       </c>
       <c r="F763">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="764" spans="1:6" x14ac:dyDescent="0.45">
@@ -15744,7 +15744,7 @@
         <v>828</v>
       </c>
       <c r="F764">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="765" spans="1:6" x14ac:dyDescent="0.45">
@@ -15764,7 +15764,7 @@
         <v>566</v>
       </c>
       <c r="F765">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="766" spans="1:6" x14ac:dyDescent="0.45">
@@ -15784,7 +15784,7 @@
         <v>664</v>
       </c>
       <c r="F766">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="767" spans="1:6" x14ac:dyDescent="0.45">
@@ -15804,7 +15804,7 @@
         <v>449</v>
       </c>
       <c r="F767">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="768" spans="1:6" x14ac:dyDescent="0.45">
@@ -15824,7 +15824,7 @@
         <v>556</v>
       </c>
       <c r="F768">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="769" spans="1:6" x14ac:dyDescent="0.45">
@@ -15844,7 +15844,7 @@
         <v>960</v>
       </c>
       <c r="F769">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="770" spans="1:6" x14ac:dyDescent="0.45">
@@ -15864,7 +15864,7 @@
         <v>1018</v>
       </c>
       <c r="F770">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="771" spans="1:6" x14ac:dyDescent="0.45">
@@ -15884,7 +15884,7 @@
         <v>779</v>
       </c>
       <c r="F771">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="772" spans="1:6" x14ac:dyDescent="0.45">
@@ -15904,7 +15904,7 @@
         <v>750</v>
       </c>
       <c r="F772">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="773" spans="1:6" x14ac:dyDescent="0.45">
@@ -15924,7 +15924,7 @@
         <v>910</v>
       </c>
       <c r="F773">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="774" spans="1:6" x14ac:dyDescent="0.45">
@@ -15944,7 +15944,7 @@
         <v>645</v>
       </c>
       <c r="F774">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="775" spans="1:6" x14ac:dyDescent="0.45">
@@ -15964,7 +15964,7 @@
         <v>617</v>
       </c>
       <c r="F775">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="776" spans="1:6" x14ac:dyDescent="0.45">
@@ -15984,7 +15984,7 @@
         <v>1118</v>
       </c>
       <c r="F776">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="777" spans="1:6" x14ac:dyDescent="0.45">
@@ -16004,7 +16004,7 @@
         <v>1006</v>
       </c>
       <c r="F777">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="778" spans="1:6" x14ac:dyDescent="0.45">
@@ -16024,7 +16024,7 @@
         <v>777</v>
       </c>
       <c r="F778">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="779" spans="1:6" x14ac:dyDescent="0.45">
@@ -16044,7 +16044,7 @@
         <v>640</v>
       </c>
       <c r="F779">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="780" spans="1:6" x14ac:dyDescent="0.45">
@@ -16064,7 +16064,7 @@
         <v>741</v>
       </c>
       <c r="F780">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="781" spans="1:6" x14ac:dyDescent="0.45">
@@ -16084,7 +16084,7 @@
         <v>1102</v>
       </c>
       <c r="F781">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="782" spans="1:6" x14ac:dyDescent="0.45">
@@ -16104,7 +16104,7 @@
         <v>666</v>
       </c>
       <c r="F782">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="783" spans="1:6" x14ac:dyDescent="0.45">
@@ -16124,7 +16124,7 @@
         <v>517</v>
       </c>
       <c r="F783">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="784" spans="1:6" x14ac:dyDescent="0.45">
@@ -16144,7 +16144,7 @@
         <v>706</v>
       </c>
       <c r="F784">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="785" spans="1:6" x14ac:dyDescent="0.45">
@@ -16164,7 +16164,7 @@
         <v>782</v>
       </c>
       <c r="F785">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="786" spans="1:6" x14ac:dyDescent="0.45">
@@ -16184,7 +16184,7 @@
         <v>902</v>
       </c>
       <c r="F786">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="787" spans="1:6" x14ac:dyDescent="0.45">
@@ -16204,7 +16204,7 @@
         <v>931</v>
       </c>
       <c r="F787">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="788" spans="1:6" x14ac:dyDescent="0.45">
@@ -16224,7 +16224,7 @@
         <v>935</v>
       </c>
       <c r="F788">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="789" spans="1:6" x14ac:dyDescent="0.45">
@@ -16244,7 +16244,7 @@
         <v>611</v>
       </c>
       <c r="F789">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="790" spans="1:6" x14ac:dyDescent="0.45">
@@ -16264,7 +16264,7 @@
         <v>1067</v>
       </c>
       <c r="F790">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="791" spans="1:6" x14ac:dyDescent="0.45">
@@ -16284,7 +16284,7 @@
         <v>1219</v>
       </c>
       <c r="F791">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="792" spans="1:6" x14ac:dyDescent="0.45">
@@ -16304,7 +16304,7 @@
         <v>1108</v>
       </c>
       <c r="F792">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="793" spans="1:6" x14ac:dyDescent="0.45">
@@ -16324,7 +16324,7 @@
         <v>704</v>
       </c>
       <c r="F793">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="794" spans="1:6" x14ac:dyDescent="0.45">
@@ -16344,7 +16344,7 @@
         <v>470</v>
       </c>
       <c r="F794">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="795" spans="1:6" x14ac:dyDescent="0.45">
@@ -16364,7 +16364,7 @@
         <v>757</v>
       </c>
       <c r="F795">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="796" spans="1:6" x14ac:dyDescent="0.45">
@@ -16384,7 +16384,7 @@
         <v>778</v>
       </c>
       <c r="F796">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="797" spans="1:6" x14ac:dyDescent="0.45">
@@ -16404,7 +16404,7 @@
         <v>1104</v>
       </c>
       <c r="F797">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="798" spans="1:6" x14ac:dyDescent="0.45">
@@ -16424,7 +16424,7 @@
         <v>1050</v>
       </c>
       <c r="F798">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="799" spans="1:6" x14ac:dyDescent="0.45">
@@ -16444,7 +16444,7 @@
         <v>632</v>
       </c>
       <c r="F799">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="800" spans="1:6" x14ac:dyDescent="0.45">
@@ -16464,7 +16464,7 @@
         <v>519</v>
       </c>
       <c r="F800">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="801" spans="1:6" x14ac:dyDescent="0.45">
@@ -16484,7 +16484,7 @@
         <v>647</v>
       </c>
       <c r="F801">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="802" spans="1:6" x14ac:dyDescent="0.45">
@@ -16504,7 +16504,7 @@
         <v>996</v>
       </c>
       <c r="F802">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="803" spans="1:6" x14ac:dyDescent="0.45">
@@ -16524,7 +16524,7 @@
         <v>652</v>
       </c>
       <c r="F803">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="804" spans="1:6" x14ac:dyDescent="0.45">
@@ -16544,7 +16544,7 @@
         <v>1057</v>
       </c>
       <c r="F804">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="805" spans="1:6" x14ac:dyDescent="0.45">
@@ -16564,7 +16564,7 @@
         <v>829</v>
       </c>
       <c r="F805">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="806" spans="1:6" x14ac:dyDescent="0.45">
@@ -16584,7 +16584,7 @@
         <v>514</v>
       </c>
       <c r="F806">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="807" spans="1:6" x14ac:dyDescent="0.45">
@@ -16604,7 +16604,7 @@
         <v>811</v>
       </c>
       <c r="F807">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="808" spans="1:6" x14ac:dyDescent="0.45">
@@ -16624,7 +16624,7 @@
         <v>1232</v>
       </c>
       <c r="F808">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="809" spans="1:6" x14ac:dyDescent="0.45">
@@ -16644,7 +16644,7 @@
         <v>697</v>
       </c>
       <c r="F809">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="810" spans="1:6" x14ac:dyDescent="0.45">
@@ -16664,7 +16664,7 @@
         <v>830</v>
       </c>
       <c r="F810">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="811" spans="1:6" x14ac:dyDescent="0.45">
@@ -16684,7 +16684,7 @@
         <v>943</v>
       </c>
       <c r="F811">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="812" spans="1:6" x14ac:dyDescent="0.45">
@@ -16704,7 +16704,7 @@
         <v>544</v>
       </c>
       <c r="F812">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="813" spans="1:6" x14ac:dyDescent="0.45">
@@ -16724,7 +16724,7 @@
         <v>475</v>
       </c>
       <c r="F813">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="814" spans="1:6" x14ac:dyDescent="0.45">
@@ -16744,7 +16744,7 @@
         <v>1234</v>
       </c>
       <c r="F814">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="815" spans="1:6" x14ac:dyDescent="0.45">
@@ -16764,7 +16764,7 @@
         <v>682</v>
       </c>
       <c r="F815">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="816" spans="1:6" x14ac:dyDescent="0.45">
@@ -16784,7 +16784,7 @@
         <v>800</v>
       </c>
       <c r="F816">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="817" spans="1:6" x14ac:dyDescent="0.45">
@@ -16804,7 +16804,7 @@
         <v>521</v>
       </c>
       <c r="F817">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="818" spans="1:6" x14ac:dyDescent="0.45">
@@ -16824,7 +16824,7 @@
         <v>771</v>
       </c>
       <c r="F818">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="819" spans="1:6" x14ac:dyDescent="0.45">
@@ -16844,7 +16844,7 @@
         <v>681</v>
       </c>
       <c r="F819">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="820" spans="1:6" x14ac:dyDescent="0.45">
@@ -16864,7 +16864,7 @@
         <v>815</v>
       </c>
       <c r="F820">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="821" spans="1:6" x14ac:dyDescent="0.45">
@@ -16884,7 +16884,7 @@
         <v>474</v>
       </c>
       <c r="F821">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="822" spans="1:6" x14ac:dyDescent="0.45">
@@ -16904,7 +16904,7 @@
         <v>597</v>
       </c>
       <c r="F822">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="823" spans="1:6" x14ac:dyDescent="0.45">
@@ -16924,7 +16924,7 @@
         <v>579</v>
       </c>
       <c r="F823">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="824" spans="1:6" x14ac:dyDescent="0.45">
@@ -16944,7 +16944,7 @@
         <v>1070</v>
       </c>
       <c r="F824">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="825" spans="1:6" x14ac:dyDescent="0.45">
@@ -16964,7 +16964,7 @@
         <v>1230</v>
       </c>
       <c r="F825">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="826" spans="1:6" x14ac:dyDescent="0.45">
@@ -16984,7 +16984,7 @@
         <v>912</v>
       </c>
       <c r="F826">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="827" spans="1:6" x14ac:dyDescent="0.45">
@@ -17004,7 +17004,7 @@
         <v>921</v>
       </c>
       <c r="F827">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="828" spans="1:6" x14ac:dyDescent="0.45">
@@ -17024,7 +17024,7 @@
         <v>561</v>
       </c>
       <c r="F828">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="829" spans="1:6" x14ac:dyDescent="0.45">
@@ -17044,7 +17044,7 @@
         <v>690</v>
       </c>
       <c r="F829">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="830" spans="1:6" x14ac:dyDescent="0.45">
@@ -17064,7 +17064,7 @@
         <v>817</v>
       </c>
       <c r="F830">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="831" spans="1:6" x14ac:dyDescent="0.45">
@@ -17084,7 +17084,7 @@
         <v>826</v>
       </c>
       <c r="F831">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="832" spans="1:6" x14ac:dyDescent="0.45">
@@ -17104,7 +17104,7 @@
         <v>452</v>
       </c>
       <c r="F832">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="833" spans="1:6" x14ac:dyDescent="0.45">
@@ -17124,7 +17124,7 @@
         <v>500</v>
       </c>
       <c r="F833">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="834" spans="1:6" x14ac:dyDescent="0.45">
@@ -17144,7 +17144,7 @@
         <v>1136</v>
       </c>
       <c r="F834">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="835" spans="1:6" x14ac:dyDescent="0.45">
@@ -17164,7 +17164,7 @@
         <v>1059</v>
       </c>
       <c r="F835">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="836" spans="1:6" x14ac:dyDescent="0.45">
@@ -17184,7 +17184,7 @@
         <v>716</v>
       </c>
       <c r="F836">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="837" spans="1:6" x14ac:dyDescent="0.45">
@@ -17204,7 +17204,7 @@
         <v>761</v>
       </c>
       <c r="F837">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="838" spans="1:6" x14ac:dyDescent="0.45">
@@ -17224,7 +17224,7 @@
         <v>858</v>
       </c>
       <c r="F838">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="839" spans="1:6" x14ac:dyDescent="0.45">
@@ -17244,7 +17244,7 @@
         <v>712</v>
       </c>
       <c r="F839">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="840" spans="1:6" x14ac:dyDescent="0.45">
@@ -17264,7 +17264,7 @@
         <v>1049</v>
       </c>
       <c r="F840">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="841" spans="1:6" x14ac:dyDescent="0.45">
@@ -17284,7 +17284,7 @@
         <v>1074</v>
       </c>
       <c r="F841">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="842" spans="1:6" x14ac:dyDescent="0.45">
@@ -17304,7 +17304,7 @@
         <v>696</v>
       </c>
       <c r="F842">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="843" spans="1:6" x14ac:dyDescent="0.45">
@@ -17324,7 +17324,7 @@
         <v>1209</v>
       </c>
       <c r="F843">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="844" spans="1:6" x14ac:dyDescent="0.45">
@@ -17344,7 +17344,7 @@
         <v>700</v>
       </c>
       <c r="F844">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="845" spans="1:6" x14ac:dyDescent="0.45">
@@ -17364,7 +17364,7 @@
         <v>1095</v>
       </c>
       <c r="F845">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="846" spans="1:6" x14ac:dyDescent="0.45">
@@ -17384,7 +17384,7 @@
         <v>435</v>
       </c>
       <c r="F846">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="847" spans="1:6" x14ac:dyDescent="0.45">
@@ -17404,7 +17404,7 @@
         <v>759</v>
       </c>
       <c r="F847">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="848" spans="1:6" x14ac:dyDescent="0.45">
@@ -17424,7 +17424,7 @@
         <v>908</v>
       </c>
       <c r="F848">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="849" spans="1:6" x14ac:dyDescent="0.45">
@@ -17444,7 +17444,7 @@
         <v>1035</v>
       </c>
       <c r="F849">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="850" spans="1:6" x14ac:dyDescent="0.45">
@@ -17464,7 +17464,7 @@
         <v>802</v>
       </c>
       <c r="F850">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="851" spans="1:6" x14ac:dyDescent="0.45">
@@ -17484,7 +17484,7 @@
         <v>659</v>
       </c>
       <c r="F851">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="852" spans="1:6" x14ac:dyDescent="0.45">
@@ -17504,7 +17504,7 @@
         <v>1020</v>
       </c>
       <c r="F852">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="853" spans="1:6" x14ac:dyDescent="0.45">
@@ -17524,7 +17524,7 @@
         <v>602</v>
       </c>
       <c r="F853">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="854" spans="1:6" x14ac:dyDescent="0.45">
@@ -17544,7 +17544,7 @@
         <v>876</v>
       </c>
       <c r="F854">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="855" spans="1:6" x14ac:dyDescent="0.45">
@@ -17564,7 +17564,7 @@
         <v>466</v>
       </c>
       <c r="F855">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="856" spans="1:6" x14ac:dyDescent="0.45">
@@ -17584,7 +17584,7 @@
         <v>1148</v>
       </c>
       <c r="F856">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="857" spans="1:6" x14ac:dyDescent="0.45">
@@ -17604,7 +17604,7 @@
         <v>762</v>
       </c>
       <c r="F857">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="858" spans="1:6" x14ac:dyDescent="0.45">
@@ -17624,7 +17624,7 @@
         <v>1084</v>
       </c>
       <c r="F858">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="859" spans="1:6" x14ac:dyDescent="0.45">
@@ -17644,7 +17644,7 @@
         <v>668</v>
       </c>
       <c r="F859">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="860" spans="1:6" x14ac:dyDescent="0.45">
@@ -17664,7 +17664,7 @@
         <v>560</v>
       </c>
       <c r="F860">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="861" spans="1:6" x14ac:dyDescent="0.45">
@@ -17684,7 +17684,7 @@
         <v>608</v>
       </c>
       <c r="F861">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="862" spans="1:6" x14ac:dyDescent="0.45">
@@ -17704,7 +17704,7 @@
         <v>806</v>
       </c>
       <c r="F862">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="863" spans="1:6" x14ac:dyDescent="0.45">
@@ -17724,7 +17724,7 @@
         <v>1138</v>
       </c>
       <c r="F863">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="864" spans="1:6" x14ac:dyDescent="0.45">
@@ -17744,7 +17744,7 @@
         <v>480</v>
       </c>
       <c r="F864">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="865" spans="1:6" x14ac:dyDescent="0.45">
@@ -17764,7 +17764,7 @@
         <v>578</v>
       </c>
       <c r="F865">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="866" spans="1:6" x14ac:dyDescent="0.45">
@@ -17784,7 +17784,7 @@
         <v>486</v>
       </c>
       <c r="F866">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="867" spans="1:6" x14ac:dyDescent="0.45">
@@ -17804,7 +17804,7 @@
         <v>707</v>
       </c>
       <c r="F867">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="868" spans="1:6" x14ac:dyDescent="0.45">
@@ -17824,7 +17824,7 @@
         <v>606</v>
       </c>
       <c r="F868">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="869" spans="1:6" x14ac:dyDescent="0.45">
@@ -17844,7 +17844,7 @@
         <v>951</v>
       </c>
       <c r="F869">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="870" spans="1:6" x14ac:dyDescent="0.45">
@@ -17864,7 +17864,7 @@
         <v>1075</v>
       </c>
       <c r="F870">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="871" spans="1:6" x14ac:dyDescent="0.45">
@@ -17884,7 +17884,7 @@
         <v>710</v>
       </c>
       <c r="F871">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="872" spans="1:6" x14ac:dyDescent="0.45">
@@ -17904,7 +17904,7 @@
         <v>728</v>
       </c>
       <c r="F872">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="873" spans="1:6" x14ac:dyDescent="0.45">
@@ -17924,7 +17924,7 @@
         <v>550</v>
       </c>
       <c r="F873">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="874" spans="1:6" x14ac:dyDescent="0.45">
@@ -17944,7 +17944,7 @@
         <v>545</v>
       </c>
       <c r="F874">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="875" spans="1:6" x14ac:dyDescent="0.45">
@@ -17964,7 +17964,7 @@
         <v>576</v>
       </c>
       <c r="F875">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="876" spans="1:6" x14ac:dyDescent="0.45">
@@ -17984,7 +17984,7 @@
         <v>687</v>
       </c>
       <c r="F876">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="877" spans="1:6" x14ac:dyDescent="0.45">
@@ -18004,7 +18004,7 @@
         <v>468</v>
       </c>
       <c r="F877">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="878" spans="1:6" x14ac:dyDescent="0.45">
@@ -18024,7 +18024,7 @@
         <v>892</v>
       </c>
       <c r="F878">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="879" spans="1:6" x14ac:dyDescent="0.45">
@@ -18044,7 +18044,7 @@
         <v>1048</v>
       </c>
       <c r="F879">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="880" spans="1:6" x14ac:dyDescent="0.45">
@@ -18064,7 +18064,7 @@
         <v>636</v>
       </c>
       <c r="F880">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="881" spans="1:6" x14ac:dyDescent="0.45">
@@ -18084,7 +18084,7 @@
         <v>726</v>
       </c>
       <c r="F881">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="882" spans="1:6" x14ac:dyDescent="0.45">
@@ -18104,7 +18104,7 @@
         <v>804</v>
       </c>
       <c r="F882">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="883" spans="1:6" x14ac:dyDescent="0.45">
@@ -18124,7 +18124,7 @@
         <v>865</v>
       </c>
       <c r="F883">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="884" spans="1:6" x14ac:dyDescent="0.45">
@@ -18144,7 +18144,7 @@
         <v>808</v>
       </c>
       <c r="F884">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="885" spans="1:6" x14ac:dyDescent="0.45">
@@ -18164,7 +18164,7 @@
         <v>856</v>
       </c>
       <c r="F885">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="886" spans="1:6" x14ac:dyDescent="0.45">
@@ -18184,7 +18184,7 @@
         <v>959</v>
       </c>
       <c r="F886">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="887" spans="1:6" x14ac:dyDescent="0.45">
@@ -18204,7 +18204,7 @@
         <v>1027</v>
       </c>
       <c r="F887">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="888" spans="1:6" x14ac:dyDescent="0.45">
@@ -18224,7 +18224,7 @@
         <v>758</v>
       </c>
       <c r="F888">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="889" spans="1:6" x14ac:dyDescent="0.45">
@@ -18244,7 +18244,7 @@
         <v>994</v>
       </c>
       <c r="F889">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="890" spans="1:6" x14ac:dyDescent="0.45">
@@ -18264,7 +18264,7 @@
         <v>498</v>
       </c>
       <c r="F890">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="891" spans="1:6" x14ac:dyDescent="0.45">
@@ -18284,7 +18284,7 @@
         <v>977</v>
       </c>
       <c r="F891">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="892" spans="1:6" x14ac:dyDescent="0.45">
@@ -18304,7 +18304,7 @@
         <v>515</v>
       </c>
       <c r="F892">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="893" spans="1:6" x14ac:dyDescent="0.45">
@@ -18324,7 +18324,7 @@
         <v>824</v>
       </c>
       <c r="F893">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="894" spans="1:6" x14ac:dyDescent="0.45">
@@ -18344,7 +18344,7 @@
         <v>965</v>
       </c>
       <c r="F894">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="895" spans="1:6" x14ac:dyDescent="0.45">
@@ -18364,7 +18364,7 @@
         <v>1088</v>
       </c>
       <c r="F895">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="896" spans="1:6" x14ac:dyDescent="0.45">
@@ -18384,7 +18384,7 @@
         <v>1182</v>
       </c>
       <c r="F896">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="897" spans="1:6" x14ac:dyDescent="0.45">
@@ -18404,7 +18404,7 @@
         <v>1121</v>
       </c>
       <c r="F897">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="898" spans="1:6" x14ac:dyDescent="0.45">
@@ -18424,7 +18424,7 @@
         <v>680</v>
       </c>
       <c r="F898">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="899" spans="1:6" x14ac:dyDescent="0.45">
@@ -18444,7 +18444,7 @@
         <v>799</v>
       </c>
       <c r="F899">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="900" spans="1:6" x14ac:dyDescent="0.45">
@@ -18464,7 +18464,7 @@
         <v>1171</v>
       </c>
       <c r="F900">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="901" spans="1:6" x14ac:dyDescent="0.45">
@@ -18484,7 +18484,7 @@
         <v>1082</v>
       </c>
       <c r="F901">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="902" spans="1:6" x14ac:dyDescent="0.45">
@@ -18504,7 +18504,7 @@
         <v>1040</v>
       </c>
       <c r="F902">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="903" spans="1:6" x14ac:dyDescent="0.45">
@@ -18524,7 +18524,7 @@
         <v>809</v>
       </c>
       <c r="F903">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="904" spans="1:6" x14ac:dyDescent="0.45">
@@ -18544,7 +18544,7 @@
         <v>532</v>
       </c>
       <c r="F904">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="905" spans="1:6" x14ac:dyDescent="0.45">
@@ -18564,7 +18564,7 @@
         <v>871</v>
       </c>
       <c r="F905">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="906" spans="1:6" x14ac:dyDescent="0.45">
@@ -18584,7 +18584,7 @@
         <v>1060</v>
       </c>
       <c r="F906">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="907" spans="1:6" x14ac:dyDescent="0.45">
@@ -18604,7 +18604,7 @@
         <v>493</v>
       </c>
       <c r="F907">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="908" spans="1:6" x14ac:dyDescent="0.45">
@@ -18624,7 +18624,7 @@
         <v>805</v>
       </c>
       <c r="F908">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="909" spans="1:6" x14ac:dyDescent="0.45">
@@ -18644,7 +18644,7 @@
         <v>490</v>
       </c>
       <c r="F909">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="910" spans="1:6" x14ac:dyDescent="0.45">
@@ -18664,7 +18664,7 @@
         <v>938</v>
       </c>
       <c r="F910">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="911" spans="1:6" x14ac:dyDescent="0.45">
@@ -18684,7 +18684,7 @@
         <v>600</v>
       </c>
       <c r="F911">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="912" spans="1:6" x14ac:dyDescent="0.45">
@@ -18704,7 +18704,7 @@
         <v>835</v>
       </c>
       <c r="F912">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="913" spans="1:6" x14ac:dyDescent="0.45">
@@ -18724,7 +18724,7 @@
         <v>1201</v>
       </c>
       <c r="F913">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="914" spans="1:6" x14ac:dyDescent="0.45">
@@ -18744,7 +18744,7 @@
         <v>1045</v>
       </c>
       <c r="F914">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="915" spans="1:6" x14ac:dyDescent="0.45">
@@ -18764,7 +18764,7 @@
         <v>889</v>
       </c>
       <c r="F915">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="916" spans="1:6" x14ac:dyDescent="0.45">
@@ -18784,7 +18784,7 @@
         <v>492</v>
       </c>
       <c r="F916">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="917" spans="1:6" x14ac:dyDescent="0.45">
@@ -18804,7 +18804,7 @@
         <v>1077</v>
       </c>
       <c r="F917">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="918" spans="1:6" x14ac:dyDescent="0.45">
@@ -18824,7 +18824,7 @@
         <v>620</v>
       </c>
       <c r="F918">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="919" spans="1:6" x14ac:dyDescent="0.45">
@@ -18844,7 +18844,7 @@
         <v>591</v>
       </c>
       <c r="F919">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="920" spans="1:6" x14ac:dyDescent="0.45">
@@ -18864,7 +18864,7 @@
         <v>962</v>
       </c>
       <c r="F920">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="921" spans="1:6" x14ac:dyDescent="0.45">
@@ -18884,7 +18884,7 @@
         <v>780</v>
       </c>
       <c r="F921">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="922" spans="1:6" x14ac:dyDescent="0.45">
@@ -18904,7 +18904,7 @@
         <v>663</v>
       </c>
       <c r="F922">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="923" spans="1:6" x14ac:dyDescent="0.45">
@@ -18924,7 +18924,7 @@
         <v>1092</v>
       </c>
       <c r="F923">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="924" spans="1:6" x14ac:dyDescent="0.45">
@@ -18944,7 +18944,7 @@
         <v>888</v>
       </c>
       <c r="F924">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="925" spans="1:6" x14ac:dyDescent="0.45">
@@ -18964,7 +18964,7 @@
         <v>973</v>
       </c>
       <c r="F925">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="926" spans="1:6" x14ac:dyDescent="0.45">
@@ -18984,7 +18984,7 @@
         <v>831</v>
       </c>
       <c r="F926">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="927" spans="1:6" x14ac:dyDescent="0.45">
@@ -19004,7 +19004,7 @@
         <v>523</v>
       </c>
       <c r="F927">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="928" spans="1:6" x14ac:dyDescent="0.45">
@@ -19024,7 +19024,7 @@
         <v>1193</v>
       </c>
       <c r="F928">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="929" spans="1:6" x14ac:dyDescent="0.45">
@@ -19044,7 +19044,7 @@
         <v>950</v>
       </c>
       <c r="F929">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="930" spans="1:6" x14ac:dyDescent="0.45">
@@ -19064,7 +19064,7 @@
         <v>586</v>
       </c>
       <c r="F930">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="931" spans="1:6" x14ac:dyDescent="0.45">
@@ -19084,7 +19084,7 @@
         <v>719</v>
       </c>
       <c r="F931">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="932" spans="1:6" x14ac:dyDescent="0.45">
@@ -19104,7 +19104,7 @@
         <v>862</v>
       </c>
       <c r="F932">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="933" spans="1:6" x14ac:dyDescent="0.45">
@@ -19124,7 +19124,7 @@
         <v>863</v>
       </c>
       <c r="F933">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="934" spans="1:6" x14ac:dyDescent="0.45">
@@ -19144,7 +19144,7 @@
         <v>846</v>
       </c>
       <c r="F934">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="935" spans="1:6" x14ac:dyDescent="0.45">
@@ -19164,7 +19164,7 @@
         <v>1159</v>
       </c>
       <c r="F935">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="936" spans="1:6" x14ac:dyDescent="0.45">
@@ -19184,7 +19184,7 @@
         <v>1087</v>
       </c>
       <c r="F936">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="937" spans="1:6" x14ac:dyDescent="0.45">
@@ -19204,7 +19204,7 @@
         <v>723</v>
       </c>
       <c r="F937">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="938" spans="1:6" x14ac:dyDescent="0.45">
@@ -19224,7 +19224,7 @@
         <v>921</v>
       </c>
       <c r="F938">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="939" spans="1:6" x14ac:dyDescent="0.45">
@@ -19244,7 +19244,7 @@
         <v>1212</v>
       </c>
       <c r="F939">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="940" spans="1:6" x14ac:dyDescent="0.45">
@@ -19264,7 +19264,7 @@
         <v>619</v>
       </c>
       <c r="F940">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="941" spans="1:6" x14ac:dyDescent="0.45">
@@ -19284,7 +19284,7 @@
         <v>1191</v>
       </c>
       <c r="F941">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="942" spans="1:6" x14ac:dyDescent="0.45">
@@ -19304,7 +19304,7 @@
         <v>1013</v>
       </c>
       <c r="F942">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="943" spans="1:6" x14ac:dyDescent="0.45">
@@ -19324,7 +19324,7 @@
         <v>1068</v>
       </c>
       <c r="F943">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="944" spans="1:6" x14ac:dyDescent="0.45">
@@ -19344,7 +19344,7 @@
         <v>1036</v>
       </c>
       <c r="F944">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="945" spans="1:6" x14ac:dyDescent="0.45">
@@ -19364,7 +19364,7 @@
         <v>1167</v>
       </c>
       <c r="F945">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="946" spans="1:6" x14ac:dyDescent="0.45">
@@ -19384,7 +19384,7 @@
         <v>387</v>
       </c>
       <c r="F946">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="947" spans="1:6" x14ac:dyDescent="0.45">
@@ -19404,7 +19404,7 @@
         <v>1129</v>
       </c>
       <c r="F947">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="948" spans="1:6" x14ac:dyDescent="0.45">
@@ -19424,7 +19424,7 @@
         <v>848</v>
       </c>
       <c r="F948">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="949" spans="1:6" x14ac:dyDescent="0.45">
@@ -19444,7 +19444,7 @@
         <v>551</v>
       </c>
       <c r="F949">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="950" spans="1:6" x14ac:dyDescent="0.45">
@@ -19464,7 +19464,7 @@
         <v>1004</v>
       </c>
       <c r="F950">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="951" spans="1:6" x14ac:dyDescent="0.45">
@@ -19484,7 +19484,7 @@
         <v>614</v>
       </c>
       <c r="F951">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="952" spans="1:6" x14ac:dyDescent="0.45">
@@ -19504,7 +19504,7 @@
         <v>616</v>
       </c>
       <c r="F952">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="953" spans="1:6" x14ac:dyDescent="0.45">
@@ -19524,7 +19524,7 @@
         <v>1206</v>
       </c>
       <c r="F953">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="954" spans="1:6" x14ac:dyDescent="0.45">
@@ -19544,7 +19544,7 @@
         <v>1173</v>
       </c>
       <c r="F954">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="955" spans="1:6" x14ac:dyDescent="0.45">
@@ -19564,7 +19564,7 @@
         <v>482</v>
       </c>
       <c r="F955">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="956" spans="1:6" x14ac:dyDescent="0.45">
@@ -19584,7 +19584,7 @@
         <v>788</v>
       </c>
       <c r="F956">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="957" spans="1:6" x14ac:dyDescent="0.45">
@@ -19604,7 +19604,7 @@
         <v>524</v>
       </c>
       <c r="F957">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="958" spans="1:6" x14ac:dyDescent="0.45">
@@ -19624,7 +19624,7 @@
         <v>942</v>
       </c>
       <c r="F958">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="959" spans="1:6" x14ac:dyDescent="0.45">
@@ -19644,7 +19644,7 @@
         <v>1072</v>
       </c>
       <c r="F959">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="960" spans="1:6" x14ac:dyDescent="0.45">
@@ -19664,7 +19664,7 @@
         <v>749</v>
       </c>
       <c r="F960">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="961" spans="1:6" x14ac:dyDescent="0.45">
@@ -19684,7 +19684,7 @@
         <v>547</v>
       </c>
       <c r="F961">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="962" spans="1:6" x14ac:dyDescent="0.45">
@@ -19704,7 +19704,7 @@
         <v>956</v>
       </c>
       <c r="F962">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="963" spans="1:6" x14ac:dyDescent="0.45">
@@ -19724,7 +19724,7 @@
         <v>1008</v>
       </c>
       <c r="F963">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="964" spans="1:6" x14ac:dyDescent="0.45">
@@ -19744,7 +19744,7 @@
         <v>727</v>
       </c>
       <c r="F964">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="965" spans="1:6" x14ac:dyDescent="0.45">
@@ -19764,7 +19764,7 @@
         <v>528</v>
       </c>
       <c r="F965">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="966" spans="1:6" x14ac:dyDescent="0.45">
@@ -19784,7 +19784,7 @@
         <v>615</v>
       </c>
       <c r="F966">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="967" spans="1:6" x14ac:dyDescent="0.45">
@@ -19804,7 +19804,7 @@
         <v>693</v>
       </c>
       <c r="F967">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="968" spans="1:6" x14ac:dyDescent="0.45">
@@ -19824,7 +19824,7 @@
         <v>1122</v>
       </c>
       <c r="F968">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="969" spans="1:6" x14ac:dyDescent="0.45">
@@ -19844,7 +19844,7 @@
         <v>760</v>
       </c>
       <c r="F969">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="970" spans="1:6" x14ac:dyDescent="0.45">
@@ -19864,7 +19864,7 @@
         <v>867</v>
       </c>
       <c r="F970">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="971" spans="1:6" x14ac:dyDescent="0.45">
@@ -19884,7 +19884,7 @@
         <v>824</v>
       </c>
       <c r="F971">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="972" spans="1:6" x14ac:dyDescent="0.45">
@@ -19904,7 +19904,7 @@
         <v>730</v>
       </c>
       <c r="F972">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="973" spans="1:6" x14ac:dyDescent="0.45">
@@ -19924,7 +19924,7 @@
         <v>755</v>
       </c>
       <c r="F973">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="974" spans="1:6" x14ac:dyDescent="0.45">
@@ -19944,7 +19944,7 @@
         <v>850</v>
       </c>
       <c r="F974">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="975" spans="1:6" x14ac:dyDescent="0.45">
@@ -19964,7 +19964,7 @@
         <v>1213</v>
       </c>
       <c r="F975">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="976" spans="1:6" x14ac:dyDescent="0.45">
@@ -19984,7 +19984,7 @@
         <v>526</v>
       </c>
       <c r="F976">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="977" spans="1:6" x14ac:dyDescent="0.45">
@@ -20004,7 +20004,7 @@
         <v>654</v>
       </c>
       <c r="F977">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="978" spans="1:6" x14ac:dyDescent="0.45">
@@ -20024,7 +20024,7 @@
         <v>967</v>
       </c>
       <c r="F978">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="979" spans="1:6" x14ac:dyDescent="0.45">
@@ -20044,7 +20044,7 @@
         <v>975</v>
       </c>
       <c r="F979">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="980" spans="1:6" x14ac:dyDescent="0.45">
@@ -20064,7 +20064,7 @@
         <v>623</v>
       </c>
       <c r="F980">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="981" spans="1:6" x14ac:dyDescent="0.45">
@@ -20084,7 +20084,7 @@
         <v>585</v>
       </c>
       <c r="F981">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="982" spans="1:6" x14ac:dyDescent="0.45">
@@ -20104,7 +20104,7 @@
         <v>720</v>
       </c>
       <c r="F982">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="983" spans="1:6" x14ac:dyDescent="0.45">
@@ -20124,7 +20124,7 @@
         <v>1207</v>
       </c>
       <c r="F983">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="984" spans="1:6" x14ac:dyDescent="0.45">
@@ -20144,7 +20144,7 @@
         <v>626</v>
       </c>
       <c r="F984">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="985" spans="1:6" x14ac:dyDescent="0.45">
@@ -20164,7 +20164,7 @@
         <v>1001</v>
       </c>
       <c r="F985">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="986" spans="1:6" x14ac:dyDescent="0.45">
@@ -20184,7 +20184,7 @@
         <v>612</v>
       </c>
       <c r="F986">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="987" spans="1:6" x14ac:dyDescent="0.45">
@@ -20204,7 +20204,7 @@
         <v>979</v>
       </c>
       <c r="F987">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="988" spans="1:6" x14ac:dyDescent="0.45">
@@ -20224,7 +20224,7 @@
         <v>1094</v>
       </c>
       <c r="F988">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="989" spans="1:6" x14ac:dyDescent="0.45">
@@ -20244,7 +20244,7 @@
         <v>952</v>
       </c>
       <c r="F989">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="990" spans="1:6" x14ac:dyDescent="0.45">
@@ -20264,7 +20264,7 @@
         <v>983</v>
       </c>
       <c r="F990">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="991" spans="1:6" x14ac:dyDescent="0.45">
@@ -20284,7 +20284,7 @@
         <v>861</v>
       </c>
       <c r="F991">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="992" spans="1:6" x14ac:dyDescent="0.45">
@@ -20304,7 +20304,7 @@
         <v>1086</v>
       </c>
       <c r="F992">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="993" spans="1:6" x14ac:dyDescent="0.45">
@@ -20324,7 +20324,7 @@
         <v>546</v>
       </c>
       <c r="F993">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="994" spans="1:6" x14ac:dyDescent="0.45">
@@ -20344,7 +20344,7 @@
         <v>913</v>
       </c>
       <c r="F994">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="995" spans="1:6" x14ac:dyDescent="0.45">
@@ -20364,7 +20364,7 @@
         <v>593</v>
       </c>
       <c r="F995">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="996" spans="1:6" x14ac:dyDescent="0.45">
@@ -20384,7 +20384,7 @@
         <v>975</v>
       </c>
       <c r="F996">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="997" spans="1:6" x14ac:dyDescent="0.45">
@@ -20404,7 +20404,7 @@
         <v>774</v>
       </c>
       <c r="F997">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="998" spans="1:6" x14ac:dyDescent="0.45">
@@ -20424,7 +20424,7 @@
         <v>1172</v>
       </c>
       <c r="F998">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="999" spans="1:6" x14ac:dyDescent="0.45">
@@ -20444,7 +20444,7 @@
         <v>925</v>
       </c>
       <c r="F999">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1000" spans="1:6" x14ac:dyDescent="0.45">
@@ -20464,7 +20464,7 @@
         <v>1090</v>
       </c>
       <c r="F1000">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1001" spans="1:6" x14ac:dyDescent="0.45">
@@ -20484,7 +20484,7 @@
         <v>784</v>
       </c>
       <c r="F1001">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1002" spans="1:6" x14ac:dyDescent="0.45">
@@ -20504,7 +20504,7 @@
         <v>1184</v>
       </c>
       <c r="F1002">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1003" spans="1:6" x14ac:dyDescent="0.45">
@@ -20524,7 +20524,7 @@
         <v>775</v>
       </c>
       <c r="F1003">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1004" spans="1:6" x14ac:dyDescent="0.45">
@@ -20544,7 +20544,7 @@
         <v>1078</v>
       </c>
       <c r="F1004">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1005" spans="1:6" x14ac:dyDescent="0.45">
@@ -20564,7 +20564,7 @@
         <v>844</v>
       </c>
       <c r="F1005">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1006" spans="1:6" x14ac:dyDescent="0.45">
@@ -20584,7 +20584,7 @@
         <v>823</v>
       </c>
       <c r="F1006">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1007" spans="1:6" x14ac:dyDescent="0.45">
@@ -20604,7 +20604,7 @@
         <v>1126</v>
       </c>
       <c r="F1007">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1008" spans="1:6" x14ac:dyDescent="0.45">
@@ -20624,7 +20624,7 @@
         <v>1194</v>
       </c>
       <c r="F1008">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1009" spans="1:6" x14ac:dyDescent="0.45">
@@ -20644,7 +20644,7 @@
         <v>625</v>
       </c>
       <c r="F1009">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1010" spans="1:6" x14ac:dyDescent="0.45">
@@ -20664,7 +20664,7 @@
         <v>834</v>
       </c>
       <c r="F1010">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1011" spans="1:6" x14ac:dyDescent="0.45">
@@ -20684,7 +20684,7 @@
         <v>958</v>
       </c>
       <c r="F1011">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1012" spans="1:6" x14ac:dyDescent="0.45">
@@ -20704,7 +20704,7 @@
         <v>1120</v>
       </c>
       <c r="F1012">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1013" spans="1:6" x14ac:dyDescent="0.45">
@@ -20724,7 +20724,7 @@
         <v>789</v>
       </c>
       <c r="F1013">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1014" spans="1:6" x14ac:dyDescent="0.45">
@@ -20744,7 +20744,7 @@
         <v>971</v>
       </c>
       <c r="F1014">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1015" spans="1:6" x14ac:dyDescent="0.45">
@@ -20764,7 +20764,7 @@
         <v>1032</v>
       </c>
       <c r="F1015">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1016" spans="1:6" x14ac:dyDescent="0.45">
@@ -20784,7 +20784,7 @@
         <v>558</v>
       </c>
       <c r="F1016">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1017" spans="1:6" x14ac:dyDescent="0.45">
@@ -20804,7 +20804,7 @@
         <v>878</v>
       </c>
       <c r="F1017">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1018" spans="1:6" x14ac:dyDescent="0.45">
@@ -20824,7 +20824,7 @@
         <v>998</v>
       </c>
       <c r="F1018">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1019" spans="1:6" x14ac:dyDescent="0.45">
@@ -20844,7 +20844,7 @@
         <v>843</v>
       </c>
       <c r="F1019">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1020" spans="1:6" x14ac:dyDescent="0.45">
@@ -20864,7 +20864,7 @@
         <v>904</v>
       </c>
       <c r="F1020">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1021" spans="1:6" x14ac:dyDescent="0.45">
@@ -20884,7 +20884,7 @@
         <v>1128</v>
       </c>
       <c r="F1021">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1022" spans="1:6" x14ac:dyDescent="0.45">
@@ -20904,7 +20904,7 @@
         <v>1197</v>
       </c>
       <c r="F1022">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1023" spans="1:6" x14ac:dyDescent="0.45">
@@ -20924,7 +20924,7 @@
         <v>1089</v>
       </c>
       <c r="F1023">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1024" spans="1:6" x14ac:dyDescent="0.45">
@@ -20944,7 +20944,7 @@
         <v>715</v>
       </c>
       <c r="F1024">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1025" spans="1:6" x14ac:dyDescent="0.45">
@@ -20964,7 +20964,7 @@
         <v>633</v>
       </c>
       <c r="F1025">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1026" spans="1:6" x14ac:dyDescent="0.45">
@@ -20984,7 +20984,7 @@
         <v>948</v>
       </c>
       <c r="F1026">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1027" spans="1:6" x14ac:dyDescent="0.45">
@@ -21004,7 +21004,7 @@
         <v>1169</v>
       </c>
       <c r="F1027">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1028" spans="1:6" x14ac:dyDescent="0.45">
@@ -21024,7 +21024,7 @@
         <v>987</v>
       </c>
       <c r="F1028">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1029" spans="1:6" x14ac:dyDescent="0.45">
@@ -21044,7 +21044,7 @@
         <v>1231</v>
       </c>
       <c r="F1029">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1030" spans="1:6" x14ac:dyDescent="0.45">
@@ -21064,7 +21064,7 @@
         <v>562</v>
       </c>
       <c r="F1030">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1031" spans="1:6" x14ac:dyDescent="0.45">
@@ -21084,7 +21084,7 @@
         <v>765</v>
       </c>
       <c r="F1031">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1032" spans="1:6" x14ac:dyDescent="0.45">
@@ -21104,7 +21104,7 @@
         <v>634</v>
       </c>
       <c r="F1032">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1033" spans="1:6" x14ac:dyDescent="0.45">
@@ -21124,7 +21124,7 @@
         <v>453</v>
       </c>
       <c r="F1033">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1034" spans="1:6" x14ac:dyDescent="0.45">
@@ -21144,7 +21144,7 @@
         <v>495</v>
       </c>
       <c r="F1034">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1035" spans="1:6" x14ac:dyDescent="0.45">
@@ -21164,7 +21164,7 @@
         <v>937</v>
       </c>
       <c r="F1035">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1036" spans="1:6" x14ac:dyDescent="0.45">
@@ -21184,7 +21184,7 @@
         <v>981</v>
       </c>
       <c r="F1036">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1037" spans="1:6" x14ac:dyDescent="0.45">
@@ -21204,7 +21204,7 @@
         <v>1142</v>
       </c>
       <c r="F1037">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1038" spans="1:6" x14ac:dyDescent="0.45">
@@ -21224,7 +21224,7 @@
         <v>506</v>
       </c>
       <c r="F1038">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1039" spans="1:6" x14ac:dyDescent="0.45">
@@ -21244,7 +21244,7 @@
         <v>969</v>
       </c>
       <c r="F1039">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1040" spans="1:6" x14ac:dyDescent="0.45">
@@ -21264,7 +21264,7 @@
         <v>465</v>
       </c>
       <c r="F1040">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1041" spans="1:6" x14ac:dyDescent="0.45">
@@ -21284,7 +21284,7 @@
         <v>507</v>
       </c>
       <c r="F1041">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1042" spans="1:6" x14ac:dyDescent="0.45">
@@ -21304,7 +21304,7 @@
         <v>695</v>
       </c>
       <c r="F1042">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1043" spans="1:6" x14ac:dyDescent="0.45">
@@ -21324,7 +21324,7 @@
         <v>810</v>
       </c>
       <c r="F1043">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1044" spans="1:6" x14ac:dyDescent="0.45">
@@ -21344,7 +21344,7 @@
         <v>1098</v>
       </c>
       <c r="F1044">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1045" spans="1:6" x14ac:dyDescent="0.45">
@@ -21364,7 +21364,7 @@
         <v>604</v>
       </c>
       <c r="F1045">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1046" spans="1:6" x14ac:dyDescent="0.45">
@@ -21384,7 +21384,7 @@
         <v>893</v>
       </c>
       <c r="F1046">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1047" spans="1:6" x14ac:dyDescent="0.45">
@@ -21404,7 +21404,7 @@
         <v>964</v>
       </c>
       <c r="F1047">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1048" spans="1:6" x14ac:dyDescent="0.45">
@@ -21424,7 +21424,7 @@
         <v>903</v>
       </c>
       <c r="F1048">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1049" spans="1:6" x14ac:dyDescent="0.45">
@@ -21444,7 +21444,7 @@
         <v>1025</v>
       </c>
       <c r="F1049">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1050" spans="1:6" x14ac:dyDescent="0.45">
@@ -21464,7 +21464,7 @@
         <v>996</v>
       </c>
       <c r="F1050">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1051" spans="1:6" x14ac:dyDescent="0.45">
@@ -21484,7 +21484,7 @@
         <v>1149</v>
       </c>
       <c r="F1051">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1052" spans="1:6" x14ac:dyDescent="0.45">
@@ -21504,7 +21504,7 @@
         <v>630</v>
       </c>
       <c r="F1052">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1053" spans="1:6" x14ac:dyDescent="0.45">
@@ -21524,7 +21524,7 @@
         <v>1127</v>
       </c>
       <c r="F1053">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1054" spans="1:6" x14ac:dyDescent="0.45">
@@ -21544,7 +21544,7 @@
         <v>879</v>
       </c>
       <c r="F1054">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1055" spans="1:6" x14ac:dyDescent="0.45">
@@ -21564,7 +21564,7 @@
         <v>796</v>
       </c>
       <c r="F1055">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1056" spans="1:6" x14ac:dyDescent="0.45">
@@ -21584,7 +21584,7 @@
         <v>1147</v>
       </c>
       <c r="F1056">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1057" spans="1:6" x14ac:dyDescent="0.45">
@@ -21604,7 +21604,7 @@
         <v>499</v>
       </c>
       <c r="F1057">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1058" spans="1:6" x14ac:dyDescent="0.45">
@@ -21624,7 +21624,7 @@
         <v>694</v>
       </c>
       <c r="F1058">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1059" spans="1:6" x14ac:dyDescent="0.45">
@@ -21644,7 +21644,7 @@
         <v>702</v>
       </c>
       <c r="F1059">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1060" spans="1:6" x14ac:dyDescent="0.45">
@@ -21664,7 +21664,7 @@
         <v>488</v>
       </c>
       <c r="F1060">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1061" spans="1:6" x14ac:dyDescent="0.45">
@@ -21684,7 +21684,7 @@
         <v>501</v>
       </c>
       <c r="F1061">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1062" spans="1:6" x14ac:dyDescent="0.45">
@@ -21704,7 +21704,7 @@
         <v>1115</v>
       </c>
       <c r="F1062">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1063" spans="1:6" x14ac:dyDescent="0.45">
@@ -21724,7 +21724,7 @@
         <v>1181</v>
       </c>
       <c r="F1063">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1064" spans="1:6" x14ac:dyDescent="0.45">
@@ -21744,7 +21744,7 @@
         <v>516</v>
       </c>
       <c r="F1064">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1065" spans="1:6" x14ac:dyDescent="0.45">
@@ -21764,7 +21764,7 @@
         <v>628</v>
       </c>
       <c r="F1065">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1066" spans="1:6" x14ac:dyDescent="0.45">
@@ -21784,7 +21784,7 @@
         <v>567</v>
       </c>
       <c r="F1066">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1067" spans="1:6" x14ac:dyDescent="0.45">
@@ -21804,7 +21804,7 @@
         <v>807</v>
       </c>
       <c r="F1067">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1068" spans="1:6" x14ac:dyDescent="0.45">
@@ -21824,7 +21824,7 @@
         <v>1217</v>
       </c>
       <c r="F1068">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1069" spans="1:6" x14ac:dyDescent="0.45">
@@ -21844,7 +21844,7 @@
         <v>877</v>
       </c>
       <c r="F1069">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1070" spans="1:6" x14ac:dyDescent="0.45">
@@ -21864,7 +21864,7 @@
         <v>797</v>
       </c>
       <c r="F1070">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1071" spans="1:6" x14ac:dyDescent="0.45">
@@ -21884,7 +21884,7 @@
         <v>869</v>
       </c>
       <c r="F1071">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1072" spans="1:6" x14ac:dyDescent="0.45">
@@ -21904,7 +21904,7 @@
         <v>1110</v>
       </c>
       <c r="F1072">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1073" spans="1:6" x14ac:dyDescent="0.45">
@@ -21924,7 +21924,7 @@
         <v>840</v>
       </c>
       <c r="F1073">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1074" spans="1:6" x14ac:dyDescent="0.45">
@@ -21944,7 +21944,7 @@
         <v>529</v>
       </c>
       <c r="F1074">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1075" spans="1:6" x14ac:dyDescent="0.45">
@@ -21964,7 +21964,7 @@
         <v>936</v>
       </c>
       <c r="F1075">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1076" spans="1:6" x14ac:dyDescent="0.45">
@@ -21984,7 +21984,7 @@
         <v>866</v>
       </c>
       <c r="F1076">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1077" spans="1:6" x14ac:dyDescent="0.45">
@@ -22004,7 +22004,7 @@
         <v>1017</v>
       </c>
       <c r="F1077">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1078" spans="1:6" x14ac:dyDescent="0.45">
@@ -22024,7 +22024,7 @@
         <v>857</v>
       </c>
       <c r="F1078">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1079" spans="1:6" x14ac:dyDescent="0.45">
@@ -22044,7 +22044,7 @@
         <v>639</v>
       </c>
       <c r="F1079">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1080" spans="1:6" x14ac:dyDescent="0.45">
@@ -22064,7 +22064,7 @@
         <v>1216</v>
       </c>
       <c r="F1080">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1081" spans="1:6" x14ac:dyDescent="0.45">
@@ -22084,7 +22084,7 @@
         <v>1125</v>
       </c>
       <c r="F1081">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1082" spans="1:6" x14ac:dyDescent="0.45">
@@ -22104,7 +22104,7 @@
         <v>873</v>
       </c>
       <c r="F1082">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1083" spans="1:6" x14ac:dyDescent="0.45">
@@ -22124,7 +22124,7 @@
         <v>553</v>
       </c>
       <c r="F1083">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1084" spans="1:6" x14ac:dyDescent="0.45">
@@ -22144,7 +22144,7 @@
         <v>756</v>
       </c>
       <c r="F1084">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1085" spans="1:6" x14ac:dyDescent="0.45">
@@ -22164,7 +22164,7 @@
         <v>1220</v>
       </c>
       <c r="F1085">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1086" spans="1:6" x14ac:dyDescent="0.45">
@@ -22184,7 +22184,7 @@
         <v>618</v>
       </c>
       <c r="F1086">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1087" spans="1:6" x14ac:dyDescent="0.45">
@@ -22204,7 +22204,7 @@
         <v>1055</v>
       </c>
       <c r="F1087">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1088" spans="1:6" x14ac:dyDescent="0.45">
@@ -22224,7 +22224,7 @@
         <v>754</v>
       </c>
       <c r="F1088">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1089" spans="1:6" x14ac:dyDescent="0.45">
@@ -22244,7 +22244,7 @@
         <v>1146</v>
       </c>
       <c r="F1089">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1090" spans="1:6" x14ac:dyDescent="0.45">
@@ -22264,7 +22264,7 @@
         <v>1141</v>
       </c>
       <c r="F1090">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1091" spans="1:6" x14ac:dyDescent="0.45">
@@ -22284,7 +22284,7 @@
         <v>1003</v>
       </c>
       <c r="F1091">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1092" spans="1:6" x14ac:dyDescent="0.45">
@@ -22304,7 +22304,7 @@
         <v>753</v>
       </c>
       <c r="F1092">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1093" spans="1:6" x14ac:dyDescent="0.45">
@@ -22324,7 +22324,7 @@
         <v>1186</v>
       </c>
       <c r="F1093">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1094" spans="1:6" x14ac:dyDescent="0.45">
@@ -22344,7 +22344,7 @@
         <v>1235</v>
       </c>
       <c r="F1094">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1095" spans="1:6" x14ac:dyDescent="0.45">
@@ -22364,7 +22364,7 @@
         <v>1124</v>
       </c>
       <c r="F1095">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1096" spans="1:6" x14ac:dyDescent="0.45">
@@ -22384,7 +22384,7 @@
         <v>582</v>
       </c>
       <c r="F1096">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1097" spans="1:6" x14ac:dyDescent="0.45">
@@ -22404,7 +22404,7 @@
         <v>573</v>
       </c>
       <c r="F1097">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1098" spans="1:6" x14ac:dyDescent="0.45">
@@ -22424,7 +22424,7 @@
         <v>691</v>
       </c>
       <c r="F1098">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1099" spans="1:6" x14ac:dyDescent="0.45">
@@ -22444,7 +22444,7 @@
         <v>1034</v>
       </c>
       <c r="F1099">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1100" spans="1:6" x14ac:dyDescent="0.45">
@@ -22464,7 +22464,7 @@
         <v>738</v>
       </c>
       <c r="F1100">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1101" spans="1:6" x14ac:dyDescent="0.45">
@@ -22484,7 +22484,7 @@
         <v>1042</v>
       </c>
       <c r="F1101">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1102" spans="1:6" x14ac:dyDescent="0.45">
@@ -22504,7 +22504,7 @@
         <v>963</v>
       </c>
       <c r="F1102">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1103" spans="1:6" x14ac:dyDescent="0.45">
@@ -22524,7 +22524,7 @@
         <v>1041</v>
       </c>
       <c r="F1103">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1104" spans="1:6" x14ac:dyDescent="0.45">
@@ -22544,7 +22544,7 @@
         <v>1132</v>
       </c>
       <c r="F1104">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1105" spans="1:6" x14ac:dyDescent="0.45">
@@ -22564,7 +22564,7 @@
         <v>1139</v>
       </c>
       <c r="F1105">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1106" spans="1:6" x14ac:dyDescent="0.45">
@@ -22584,7 +22584,7 @@
         <v>1166</v>
       </c>
       <c r="F1106">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1107" spans="1:6" x14ac:dyDescent="0.45">
@@ -22604,7 +22604,7 @@
         <v>1096</v>
       </c>
       <c r="F1107">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1108" spans="1:6" x14ac:dyDescent="0.45">
@@ -22624,7 +22624,7 @@
         <v>919</v>
       </c>
       <c r="F1108">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1109" spans="1:6" x14ac:dyDescent="0.45">
@@ -22644,7 +22644,7 @@
         <v>722</v>
       </c>
       <c r="F1109">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1110" spans="1:6" x14ac:dyDescent="0.45">
@@ -22664,7 +22664,7 @@
         <v>914</v>
       </c>
       <c r="F1110">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1111" spans="1:6" x14ac:dyDescent="0.45">
@@ -22684,7 +22684,7 @@
         <v>864</v>
       </c>
       <c r="F1111">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1112" spans="1:6" x14ac:dyDescent="0.45">
@@ -22704,7 +22704,7 @@
         <v>688</v>
       </c>
       <c r="F1112">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1113" spans="1:6" x14ac:dyDescent="0.45">
@@ -22724,7 +22724,7 @@
         <v>787</v>
       </c>
       <c r="F1113">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1114" spans="1:6" x14ac:dyDescent="0.45">
@@ -22744,7 +22744,7 @@
         <v>467</v>
       </c>
       <c r="F1114">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1115" spans="1:6" x14ac:dyDescent="0.45">
@@ -22764,7 +22764,7 @@
         <v>894</v>
       </c>
       <c r="F1115">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1116" spans="1:6" x14ac:dyDescent="0.45">
@@ -22784,7 +22784,7 @@
         <v>1203</v>
       </c>
       <c r="F1116">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1117" spans="1:6" x14ac:dyDescent="0.45">
@@ -22804,7 +22804,7 @@
         <v>1065</v>
       </c>
       <c r="F1117">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1118" spans="1:6" x14ac:dyDescent="0.45">
@@ -22824,7 +22824,7 @@
         <v>1112</v>
       </c>
       <c r="F1118">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1119" spans="1:6" x14ac:dyDescent="0.45">
@@ -22844,7 +22844,7 @@
         <v>990</v>
       </c>
       <c r="F1119">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1120" spans="1:6" x14ac:dyDescent="0.45">
@@ -22864,7 +22864,7 @@
         <v>1218</v>
       </c>
       <c r="F1120">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1121" spans="1:6" x14ac:dyDescent="0.45">
@@ -22884,7 +22884,7 @@
         <v>745</v>
       </c>
       <c r="F1121">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1122" spans="1:6" x14ac:dyDescent="0.45">
@@ -22904,7 +22904,7 @@
         <v>1161</v>
       </c>
       <c r="F1122">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1123" spans="1:6" x14ac:dyDescent="0.45">
@@ -22924,7 +22924,7 @@
         <v>798</v>
       </c>
       <c r="F1123">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1124" spans="1:6" x14ac:dyDescent="0.45">
@@ -22944,7 +22944,7 @@
         <v>776</v>
       </c>
       <c r="F1124">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1125" spans="1:6" x14ac:dyDescent="0.45">
@@ -22964,7 +22964,7 @@
         <v>872</v>
       </c>
       <c r="F1125">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1126" spans="1:6" x14ac:dyDescent="0.45">
@@ -22984,7 +22984,7 @@
         <v>1062</v>
       </c>
       <c r="F1126">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1127" spans="1:6" x14ac:dyDescent="0.45">
@@ -23004,7 +23004,7 @@
         <v>1152</v>
       </c>
       <c r="F1127">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1128" spans="1:6" x14ac:dyDescent="0.45">
@@ -23024,7 +23024,7 @@
         <v>708</v>
       </c>
       <c r="F1128">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1129" spans="1:6" x14ac:dyDescent="0.45">
@@ -23044,7 +23044,7 @@
         <v>972</v>
       </c>
       <c r="F1129">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1130" spans="1:6" x14ac:dyDescent="0.45">
@@ -23064,7 +23064,7 @@
         <v>837</v>
       </c>
       <c r="F1130">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1131" spans="1:6" x14ac:dyDescent="0.45">
@@ -23084,7 +23084,7 @@
         <v>736</v>
       </c>
       <c r="F1131">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1132" spans="1:6" x14ac:dyDescent="0.45">
@@ -23104,7 +23104,7 @@
         <v>699</v>
       </c>
       <c r="F1132">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1133" spans="1:6" x14ac:dyDescent="0.45">
@@ -23124,7 +23124,7 @@
         <v>814</v>
       </c>
       <c r="F1133">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1134" spans="1:6" x14ac:dyDescent="0.45">
@@ -23144,7 +23144,7 @@
         <v>812</v>
       </c>
       <c r="F1134">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1135" spans="1:6" x14ac:dyDescent="0.45">
@@ -23164,7 +23164,7 @@
         <v>1100</v>
       </c>
       <c r="F1135">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1136" spans="1:6" x14ac:dyDescent="0.45">
@@ -23184,7 +23184,7 @@
         <v>1196</v>
       </c>
       <c r="F1136">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1137" spans="1:6" x14ac:dyDescent="0.45">
@@ -23204,7 +23204,7 @@
         <v>684</v>
       </c>
       <c r="F1137">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1138" spans="1:6" x14ac:dyDescent="0.45">
@@ -23224,7 +23224,7 @@
         <v>662</v>
       </c>
       <c r="F1138">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1139" spans="1:6" x14ac:dyDescent="0.45">
@@ -23244,7 +23244,7 @@
         <v>1185</v>
       </c>
       <c r="F1139">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1140" spans="1:6" x14ac:dyDescent="0.45">
@@ -23264,7 +23264,7 @@
         <v>1099</v>
       </c>
       <c r="F1140">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1141" spans="1:6" x14ac:dyDescent="0.45">
@@ -23284,7 +23284,7 @@
         <v>1214</v>
       </c>
       <c r="F1141">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1142" spans="1:6" x14ac:dyDescent="0.45">
@@ -23304,7 +23304,7 @@
         <v>766</v>
       </c>
       <c r="F1142">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1143" spans="1:6" x14ac:dyDescent="0.45">
@@ -23324,7 +23324,7 @@
         <v>1140</v>
       </c>
       <c r="F1143">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1144" spans="1:6" x14ac:dyDescent="0.45">
@@ -23344,7 +23344,7 @@
         <v>675</v>
       </c>
       <c r="F1144">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1145" spans="1:6" x14ac:dyDescent="0.45">
@@ -23364,7 +23364,7 @@
         <v>1123</v>
       </c>
       <c r="F1145">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1146" spans="1:6" x14ac:dyDescent="0.45">
@@ -23384,7 +23384,7 @@
         <v>711</v>
       </c>
       <c r="F1146">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1147" spans="1:6" x14ac:dyDescent="0.45">
@@ -23404,7 +23404,7 @@
         <v>1226</v>
       </c>
       <c r="F1147">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1148" spans="1:6" x14ac:dyDescent="0.45">
@@ -23424,7 +23424,7 @@
         <v>1012</v>
       </c>
       <c r="F1148">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1149" spans="1:6" x14ac:dyDescent="0.45">
@@ -23444,7 +23444,7 @@
         <v>794</v>
       </c>
       <c r="F1149">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1150" spans="1:6" x14ac:dyDescent="0.45">
@@ -23464,7 +23464,7 @@
         <v>445</v>
       </c>
       <c r="F1150">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1151" spans="1:6" x14ac:dyDescent="0.45">
@@ -23484,7 +23484,7 @@
         <v>955</v>
       </c>
       <c r="F1151">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1152" spans="1:6" x14ac:dyDescent="0.45">
@@ -23504,7 +23504,7 @@
         <v>438</v>
       </c>
       <c r="F1152">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1153" spans="1:6" x14ac:dyDescent="0.45">
@@ -23524,7 +23524,7 @@
         <v>1237</v>
       </c>
       <c r="F1153">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1154" spans="1:6" x14ac:dyDescent="0.45">
@@ -23544,7 +23544,7 @@
         <v>821</v>
       </c>
       <c r="F1154">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1155" spans="1:6" x14ac:dyDescent="0.45">
@@ -23564,7 +23564,7 @@
         <v>1112</v>
       </c>
       <c r="F1155">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1156" spans="1:6" x14ac:dyDescent="0.45">
@@ -23584,7 +23584,7 @@
         <v>946</v>
       </c>
       <c r="F1156">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1157" spans="1:6" x14ac:dyDescent="0.45">
@@ -23604,7 +23604,7 @@
         <v>923</v>
       </c>
       <c r="F1157">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1158" spans="1:6" x14ac:dyDescent="0.45">
@@ -23624,7 +23624,7 @@
         <v>530</v>
       </c>
       <c r="F1158">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1159" spans="1:6" x14ac:dyDescent="0.45">
@@ -23644,7 +23644,7 @@
         <v>624</v>
       </c>
       <c r="F1159">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1160" spans="1:6" x14ac:dyDescent="0.45">
@@ -23664,7 +23664,7 @@
         <v>531</v>
       </c>
       <c r="F1160">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1161" spans="1:6" x14ac:dyDescent="0.45">
@@ -23684,7 +23684,7 @@
         <v>1233</v>
       </c>
       <c r="F1161">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1162" spans="1:6" x14ac:dyDescent="0.45">
@@ -23704,7 +23704,7 @@
         <v>988</v>
       </c>
       <c r="F1162">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1163" spans="1:6" x14ac:dyDescent="0.45">
@@ -23724,7 +23724,7 @@
         <v>497</v>
       </c>
       <c r="F1163">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1164" spans="1:6" x14ac:dyDescent="0.45">
@@ -23744,7 +23744,7 @@
         <v>1135</v>
       </c>
       <c r="F1164">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1165" spans="1:6" x14ac:dyDescent="0.45">
@@ -23764,7 +23764,7 @@
         <v>518</v>
       </c>
       <c r="F1165">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1166" spans="1:6" x14ac:dyDescent="0.45">
@@ -23784,7 +23784,7 @@
         <v>692</v>
       </c>
       <c r="F1166">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1167" spans="1:6" x14ac:dyDescent="0.45">
@@ -23804,7 +23804,7 @@
         <v>595</v>
       </c>
       <c r="F1167">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1168" spans="1:6" x14ac:dyDescent="0.45">
@@ -23824,7 +23824,7 @@
         <v>487</v>
       </c>
       <c r="F1168">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1169" spans="1:6" x14ac:dyDescent="0.45">
@@ -23844,7 +23844,7 @@
         <v>766</v>
       </c>
       <c r="F1169">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1170" spans="1:6" x14ac:dyDescent="0.45">
@@ -23864,7 +23864,7 @@
         <v>535</v>
       </c>
       <c r="F1170">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1171" spans="1:6" x14ac:dyDescent="0.45">
@@ -23884,7 +23884,7 @@
         <v>580</v>
       </c>
       <c r="F1171">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1172" spans="1:6" x14ac:dyDescent="0.45">
@@ -23904,7 +23904,7 @@
         <v>679</v>
       </c>
       <c r="F1172">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1173" spans="1:6" x14ac:dyDescent="0.45">
@@ -23924,7 +23924,7 @@
         <v>945</v>
       </c>
       <c r="F1173">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1174" spans="1:6" x14ac:dyDescent="0.45">
@@ -23944,7 +23944,7 @@
         <v>460</v>
       </c>
       <c r="F1174">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1175" spans="1:6" x14ac:dyDescent="0.45">
@@ -23964,7 +23964,7 @@
         <v>671</v>
       </c>
       <c r="F1175">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1176" spans="1:6" x14ac:dyDescent="0.45">
@@ -23984,7 +23984,7 @@
         <v>849</v>
       </c>
       <c r="F1176">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1177" spans="1:6" x14ac:dyDescent="0.45">
@@ -24004,7 +24004,7 @@
         <v>609</v>
       </c>
       <c r="F1177">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1178" spans="1:6" x14ac:dyDescent="0.45">
@@ -24024,7 +24024,7 @@
         <v>559</v>
       </c>
       <c r="F1178">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1179" spans="1:6" x14ac:dyDescent="0.45">
@@ -24044,7 +24044,7 @@
         <v>491</v>
       </c>
       <c r="F1179">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1180" spans="1:6" x14ac:dyDescent="0.45">
@@ -24064,7 +24064,7 @@
         <v>621</v>
       </c>
       <c r="F1180">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1181" spans="1:6" x14ac:dyDescent="0.45">
@@ -24084,7 +24084,7 @@
         <v>1156</v>
       </c>
       <c r="F1181">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1182" spans="1:6" x14ac:dyDescent="0.45">
@@ -24104,7 +24104,7 @@
         <v>1160</v>
       </c>
       <c r="F1182">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1183" spans="1:6" x14ac:dyDescent="0.45">
@@ -24124,7 +24124,7 @@
         <v>995</v>
       </c>
       <c r="F1183">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1184" spans="1:6" x14ac:dyDescent="0.45">
@@ -24144,7 +24144,7 @@
         <v>1180</v>
       </c>
       <c r="F1184">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1185" spans="1:6" x14ac:dyDescent="0.45">
@@ -24164,7 +24164,7 @@
         <v>703</v>
       </c>
       <c r="F1185">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1186" spans="1:6" x14ac:dyDescent="0.45">
@@ -24184,7 +24184,7 @@
         <v>901</v>
       </c>
       <c r="F1186">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1187" spans="1:6" x14ac:dyDescent="0.45">
@@ -24204,7 +24204,7 @@
         <v>1198</v>
       </c>
       <c r="F1187">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1188" spans="1:6" x14ac:dyDescent="0.45">
@@ -24224,7 +24224,7 @@
         <v>575</v>
       </c>
       <c r="F1188">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1189" spans="1:6" x14ac:dyDescent="0.45">
@@ -24244,7 +24244,7 @@
         <v>667</v>
       </c>
       <c r="F1189">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1190" spans="1:6" x14ac:dyDescent="0.45">
@@ -24264,7 +24264,7 @@
         <v>592</v>
       </c>
       <c r="F1190">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1191" spans="1:6" x14ac:dyDescent="0.45">
@@ -24284,7 +24284,7 @@
         <v>584</v>
       </c>
       <c r="F1191">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1192" spans="1:6" x14ac:dyDescent="0.45">
@@ -24304,7 +24304,7 @@
         <v>735</v>
       </c>
       <c r="F1192">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1193" spans="1:6" x14ac:dyDescent="0.45">
@@ -24324,7 +24324,7 @@
         <v>1105</v>
       </c>
       <c r="F1193">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1194" spans="1:6" x14ac:dyDescent="0.45">
@@ -24344,7 +24344,7 @@
         <v>436</v>
       </c>
       <c r="F1194">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1195" spans="1:6" x14ac:dyDescent="0.45">
@@ -24364,7 +24364,7 @@
         <v>1155</v>
       </c>
       <c r="F1195">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1196" spans="1:6" x14ac:dyDescent="0.45">
@@ -24384,7 +24384,7 @@
         <v>476</v>
       </c>
       <c r="F1196">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1197" spans="1:6" x14ac:dyDescent="0.45">
@@ -24404,7 +24404,7 @@
         <v>984</v>
       </c>
       <c r="F1197">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1198" spans="1:6" x14ac:dyDescent="0.45">
@@ -24424,7 +24424,7 @@
         <v>747</v>
       </c>
       <c r="F1198">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1199" spans="1:6" x14ac:dyDescent="0.45">
@@ -24444,7 +24444,7 @@
         <v>1029</v>
       </c>
       <c r="F1199">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1200" spans="1:6" x14ac:dyDescent="0.45">
@@ -24464,7 +24464,7 @@
         <v>448</v>
       </c>
       <c r="F1200">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1201" spans="1:6" x14ac:dyDescent="0.45">
@@ -24484,7 +24484,7 @@
         <v>454</v>
       </c>
       <c r="F1201">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1202" spans="1:6" x14ac:dyDescent="0.45">
@@ -24504,7 +24504,7 @@
         <v>596</v>
       </c>
       <c r="F1202">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1203" spans="1:6" x14ac:dyDescent="0.45">
@@ -24524,7 +24524,7 @@
         <v>1009</v>
       </c>
       <c r="F1203">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1204" spans="1:6" x14ac:dyDescent="0.45">
@@ -24544,7 +24544,7 @@
         <v>484</v>
       </c>
       <c r="F1204">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1205" spans="1:6" x14ac:dyDescent="0.45">
@@ -24564,7 +24564,7 @@
         <v>1056</v>
       </c>
       <c r="F1205">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1206" spans="1:6" x14ac:dyDescent="0.45">
@@ -24584,7 +24584,7 @@
         <v>447</v>
       </c>
       <c r="F1206">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1207" spans="1:6" x14ac:dyDescent="0.45">
@@ -24604,7 +24604,7 @@
         <v>999</v>
       </c>
       <c r="F1207">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1208" spans="1:6" x14ac:dyDescent="0.45">
@@ -24624,7 +24624,7 @@
         <v>1023</v>
       </c>
       <c r="F1208">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1209" spans="1:6" x14ac:dyDescent="0.45">
@@ -24644,7 +24644,7 @@
         <v>772</v>
       </c>
       <c r="F1209">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1210" spans="1:6" x14ac:dyDescent="0.45">
@@ -24664,7 +24664,7 @@
         <v>505</v>
       </c>
       <c r="F1210">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1211" spans="1:6" x14ac:dyDescent="0.45">
@@ -24684,7 +24684,7 @@
         <v>733</v>
       </c>
       <c r="F1211">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1212" spans="1:6" x14ac:dyDescent="0.45">
@@ -24704,7 +24704,7 @@
         <v>431</v>
       </c>
       <c r="F1212">
-        <v>30</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1213" spans="1:6" x14ac:dyDescent="0.45">
@@ -24724,7 +24724,7 @@
         <v>1053</v>
       </c>
       <c r="F1213">
-        <v>30</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1214" spans="1:6" x14ac:dyDescent="0.45">
@@ -24744,7 +24744,7 @@
         <v>444</v>
       </c>
       <c r="F1214">
-        <v>30</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1215" spans="1:6" x14ac:dyDescent="0.45">
@@ -24764,7 +24764,7 @@
         <v>991</v>
       </c>
       <c r="F1215">
-        <v>30</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1216" spans="1:6" x14ac:dyDescent="0.45">
@@ -24784,7 +24784,7 @@
         <v>791</v>
       </c>
       <c r="F1216">
-        <v>30</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1217" spans="1:6" x14ac:dyDescent="0.45">
@@ -24804,7 +24804,7 @@
         <v>605</v>
       </c>
       <c r="F1217">
-        <v>30</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1218" spans="1:6" x14ac:dyDescent="0.45">
@@ -24824,7 +24824,7 @@
         <v>538</v>
       </c>
       <c r="F1218">
-        <v>30</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1219" spans="1:6" x14ac:dyDescent="0.45">
@@ -24844,7 +24844,7 @@
         <v>433</v>
       </c>
       <c r="F1219">
-        <v>30</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1220" spans="1:6" x14ac:dyDescent="0.45">
@@ -24864,7 +24864,7 @@
         <v>563</v>
       </c>
       <c r="F1220">
-        <v>30</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1221" spans="1:6" x14ac:dyDescent="0.45">
@@ -24884,7 +24884,7 @@
         <v>577</v>
       </c>
       <c r="F1221">
-        <v>30</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1222" spans="1:6" x14ac:dyDescent="0.45">
@@ -24904,7 +24904,7 @@
         <v>440</v>
       </c>
       <c r="F1222">
-        <v>30</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1223" spans="1:6" x14ac:dyDescent="0.45">
@@ -24924,7 +24924,7 @@
         <v>801</v>
       </c>
       <c r="F1223">
-        <v>30</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1224" spans="1:6" x14ac:dyDescent="0.45">
@@ -24944,7 +24944,7 @@
         <v>471</v>
       </c>
       <c r="F1224">
-        <v>30</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1225" spans="1:6" x14ac:dyDescent="0.45">
@@ -24964,7 +24964,7 @@
         <v>429</v>
       </c>
       <c r="F1225">
-        <v>30</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1226" spans="1:6" x14ac:dyDescent="0.45">
@@ -24984,7 +24984,7 @@
         <v>724</v>
       </c>
       <c r="F1226">
-        <v>30</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1227" spans="1:6" x14ac:dyDescent="0.45">
@@ -25004,7 +25004,7 @@
         <v>485</v>
       </c>
       <c r="F1227">
-        <v>30</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1228" spans="1:6" x14ac:dyDescent="0.45">
@@ -25024,7 +25024,7 @@
         <v>1177</v>
       </c>
       <c r="F1228">
-        <v>30</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1229" spans="1:6" x14ac:dyDescent="0.45">
@@ -25044,7 +25044,7 @@
         <v>882</v>
       </c>
       <c r="F1229">
-        <v>30</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1230" spans="1:6" x14ac:dyDescent="0.45">
@@ -25064,7 +25064,7 @@
         <v>478</v>
       </c>
       <c r="F1230">
-        <v>30</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1231" spans="1:6" x14ac:dyDescent="0.45">
@@ -25084,7 +25084,7 @@
         <v>570</v>
       </c>
       <c r="F1231">
-        <v>30</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1232" spans="1:6" x14ac:dyDescent="0.45">
@@ -25104,7 +25104,7 @@
         <v>729</v>
       </c>
       <c r="F1232">
-        <v>30</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1233" spans="1:6" x14ac:dyDescent="0.45">
@@ -25124,7 +25124,7 @@
         <v>786</v>
       </c>
       <c r="F1233">
-        <v>30</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1234" spans="1:6" x14ac:dyDescent="0.45">
@@ -25144,7 +25144,7 @@
         <v>509</v>
       </c>
       <c r="F1234">
-        <v>30</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1235" spans="1:6" x14ac:dyDescent="0.45">
@@ -25164,7 +25164,7 @@
         <v>1222</v>
       </c>
       <c r="F1235">
-        <v>30</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1236" spans="1:6" x14ac:dyDescent="0.45">
@@ -25184,7 +25184,7 @@
         <v>522</v>
       </c>
       <c r="F1236">
-        <v>30</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1237" spans="1:6" x14ac:dyDescent="0.45">
@@ -25204,7 +25204,7 @@
         <v>1028</v>
       </c>
       <c r="F1237">
-        <v>30</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1238" spans="1:6" x14ac:dyDescent="0.45">
@@ -25224,7 +25224,7 @@
         <v>483</v>
       </c>
       <c r="F1238">
-        <v>30</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1239" spans="1:6" x14ac:dyDescent="0.45">
@@ -25244,7 +25244,7 @@
         <v>932</v>
       </c>
       <c r="F1239">
-        <v>30</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1240" spans="1:6" x14ac:dyDescent="0.45">
@@ -25264,7 +25264,7 @@
         <v>555</v>
       </c>
       <c r="F1240">
-        <v>30</v>
+        <v>750</v>
       </c>
     </row>
     <row r="1241" spans="1:6" x14ac:dyDescent="0.45">
@@ -25284,11 +25284,10 @@
         <v>1047</v>
       </c>
       <c r="F1241">
-        <v>30</v>
+        <v>750</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1241" xr:uid="{5D19D05A-7F0E-456D-A90D-5A173E8A2D3B}"/>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
